--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="common" sheetId="1" r:id="Rc5fb3d18fecb4eae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="app" sheetId="2" r:id="R427faccaff2145a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baby_recyclerview" sheetId="3" r:id="R45ae57d448ee4ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="common" sheetId="1" r:id="Rf1fd52605813477b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="app" sheetId="2" r:id="Raad3613902024864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baby_recyclerview" sheetId="3" r:id="Rd47692228b6e4dce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21654,7 +21654,7 @@
         <x:v>%1$d小时%2$d分</x:v>
       </x:c>
       <x:c r="C507" t="str">
-        <x:v>%1$dh %2$dm</x:v>
+        <x:v>%1$dH %2$dm</x:v>
       </x:c>
       <x:c r="D507" t="str">
         <x:v>%1$d小時%2$d分</x:v>
@@ -21696,7 +21696,7 @@
         <x:v>%1$d小时</x:v>
       </x:c>
       <x:c r="C508" t="str">
-        <x:v>%1$dh</x:v>
+        <x:v>%1$dH</x:v>
       </x:c>
       <x:c r="D508" t="str">
         <x:v>%1$d小時</x:v>
@@ -21735,13 +21735,13 @@
         <x:v>summary_duration_minutes_compact</x:v>
       </x:c>
       <x:c r="B509" t="str">
-        <x:v>%1$d分钟</x:v>
+        <x:v>%1$d分</x:v>
       </x:c>
       <x:c r="C509" t="str">
         <x:v>%1$dm</x:v>
       </x:c>
       <x:c r="D509" t="str">
-        <x:v>%1$d分鐘</x:v>
+        <x:v>%1$d分</x:v>
       </x:c>
       <x:c r="E509" t="str">
         <x:v>%1$d分</x:v>
@@ -21777,13 +21777,13 @@
         <x:v>summary_duration_zero_compact</x:v>
       </x:c>
       <x:c r="B510" t="str">
-        <x:v>0分钟</x:v>
+        <x:v>0分</x:v>
       </x:c>
       <x:c r="C510" t="str">
         <x:v>0m</x:v>
       </x:c>
       <x:c r="D510" t="str">
-        <x:v>0分鐘</x:v>
+        <x:v>0分</x:v>
       </x:c>
       <x:c r="E510" t="str">
         <x:v>0分</x:v>
@@ -22363,7 +22363,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12dd8bffd1cc41cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R270e3dc2e53f4d95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22533,7 +22533,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7a26ef3056846c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c4e0e6384c94c86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22829,7 +22829,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb69fdc5f3b69435f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fe23672f9f8443e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tools/language/多语言对照表.xlsx
+++ b/tools/language/多语言对照表.xlsx
@@ -389,7 +389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB530"/>
+  <dimension ref="A1:AB532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.6299991607666" customWidth="1" min="1" max="1"/>
@@ -20007,32 +20007,32 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>temperature_low_fever</t>
+          <t>temperature_low</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>低烧</t>
+          <t>偏低</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>low fever</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>低燒</t>
+          <t>偏低</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr">
         <is>
-          <t>微熱</t>
+          <t>低め</t>
         </is>
       </c>
       <c r="F362" s="4" t="inlineStr">
         <is>
-          <t>저열</t>
+          <t>낮음</t>
         </is>
       </c>
       <c r="G362" s="4" t="n"/>
@@ -20061,32 +20061,32 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>temperature_high_fever</t>
+          <t>temperature_low_warning</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>高烧</t>
+          <t>体温偏低，请注意保暖并观察</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>high fever</t>
+          <t>Temperature is low. Keep the baby warm and observe.</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>高燒</t>
+          <t>體溫偏低，請注意保暖並觀察</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
-          <t>高熱</t>
+          <t>体温が低めです。保温して様子を見てください</t>
         </is>
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>고열</t>
+          <t>체온이 낮습니다. 따뜻하게 하고 관찰하세요</t>
         </is>
       </c>
       <c r="G363" s="4" t="n"/>
@@ -20115,32 +20115,32 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>temperature_warning</t>
+          <t>temperature_low_fever</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>体温偏高，请注意观察</t>
+          <t>低烧</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>The body temperature is high, please pay attention</t>
+          <t>low fever</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>體溫偏高，請注意觀察</t>
+          <t>低燒</t>
         </is>
       </c>
       <c r="E364" s="4" t="inlineStr">
         <is>
-          <t>体温が高いので注意してください</t>
+          <t>微熱</t>
         </is>
       </c>
       <c r="F364" s="4" t="inlineStr">
         <is>
-          <t>체온이 높으니 주의해주세요</t>
+          <t>저열</t>
         </is>
       </c>
       <c r="G364" s="4" t="n"/>
@@ -20169,32 +20169,32 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>temperature_danger</t>
+          <t>temperature_high_fever</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>体温过高，建议就医</t>
+          <t>高烧</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>The body temperature is too high, it is recommended to seek medical treatment</t>
+          <t>high fever</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>體溫過高，建議就醫</t>
+          <t>高燒</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
-          <t>体温が高すぎるため、医師の治療を受けることをお勧めします</t>
+          <t>高熱</t>
         </is>
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>체온이 너무 높으므로 진료를 받는 것이 좋습니다.</t>
+          <t>고열</t>
         </is>
       </c>
       <c r="G365" s="4" t="n"/>
@@ -20223,32 +20223,32 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>temperature_location_label</t>
+          <t>temperature_warning</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>测量部位</t>
+          <t>体温偏高，请注意观察</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>The body temperature is high, please pay attention</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>測量部位</t>
+          <t>體溫偏高，請注意觀察</t>
         </is>
       </c>
       <c r="E366" s="4" t="inlineStr">
         <is>
-          <t>測定部</t>
+          <t>体温が高いので注意してください</t>
         </is>
       </c>
       <c r="F366" s="4" t="inlineStr">
         <is>
-          <t>측정부</t>
+          <t>체온이 높으니 주의해주세요</t>
         </is>
       </c>
       <c r="G366" s="4" t="n"/>
@@ -20277,32 +20277,32 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>temperature_location_ear</t>
+          <t>temperature_danger</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>耳温</t>
+          <t>体温过高，建议就医</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Ear</t>
+          <t>The body temperature is too high, it is recommended to seek medical treatment</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>耳溫</t>
+          <t>體溫過高，建議就醫</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
-          <t>耳の温度</t>
+          <t>体温が高すぎるため、医師の治療を受けることをお勧めします</t>
         </is>
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>귀 온도</t>
+          <t>체온이 너무 높으므로 진료를 받는 것이 좋습니다.</t>
         </is>
       </c>
       <c r="G367" s="4" t="n"/>
@@ -20331,32 +20331,32 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>temperature_location_forehead</t>
+          <t>temperature_location_label</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>额温</t>
+          <t>测量部位</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Forehead</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>額溫</t>
+          <t>測量部位</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr">
         <is>
-          <t>額の温度</t>
+          <t>測定部</t>
         </is>
       </c>
       <c r="F368" s="4" t="inlineStr">
         <is>
-          <t>이마 온도</t>
+          <t>측정부</t>
         </is>
       </c>
       <c r="G368" s="4" t="n"/>
@@ -20385,32 +20385,32 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>temperature_location_armpit</t>
+          <t>temperature_location_ear</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>腋温</t>
+          <t>耳温</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>Armpit</t>
+          <t>Ear</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>腋溫</t>
+          <t>耳溫</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
         <is>
-          <t>腋窩温</t>
+          <t>耳の温度</t>
         </is>
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>겨드랑이 온도</t>
+          <t>귀 온도</t>
         </is>
       </c>
       <c r="G369" s="4" t="n"/>
@@ -20439,32 +20439,32 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>temperature_location_oral</t>
+          <t>temperature_location_forehead</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>口温</t>
+          <t>额温</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Oral</t>
+          <t>Forehead</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>口溫</t>
+          <t>額溫</t>
         </is>
       </c>
       <c r="E370" s="4" t="inlineStr">
         <is>
-          <t>口腔温度</t>
+          <t>額の温度</t>
         </is>
       </c>
       <c r="F370" s="4" t="inlineStr">
         <is>
-          <t>구강 온도</t>
+          <t>이마 온도</t>
         </is>
       </c>
       <c r="G370" s="4" t="n"/>
@@ -20493,32 +20493,32 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>temperature_location_rectal</t>
+          <t>temperature_location_armpit</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>肛温</t>
+          <t>腋温</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Rectal</t>
+          <t>Armpit</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>肛溫</t>
+          <t>腋溫</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
-          <t>直腸温</t>
+          <t>腋窩温</t>
         </is>
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>직장 온도</t>
+          <t>겨드랑이 온도</t>
         </is>
       </c>
       <c r="G371" s="4" t="n"/>
@@ -20547,32 +20547,32 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>medicine_name</t>
+          <t>temperature_location_oral</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>药品名称</t>
+          <t>口温</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Drug name</t>
+          <t>Oral</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>藥品名稱</t>
+          <t>口溫</t>
         </is>
       </c>
       <c r="E372" s="4" t="inlineStr">
         <is>
-          <t>薬剤名</t>
+          <t>口腔温度</t>
         </is>
       </c>
       <c r="F372" s="4" t="inlineStr">
         <is>
-          <t>약명</t>
+          <t>구강 온도</t>
         </is>
       </c>
       <c r="G372" s="4" t="n"/>
@@ -20601,32 +20601,32 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>medicine_name_hint</t>
+          <t>temperature_location_rectal</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>请输入药品名称</t>
+          <t>肛温</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Please enter the drug name</t>
+          <t>Rectal</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>請輸入藥品名稱</t>
+          <t>肛溫</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
         <is>
-          <t>薬剤名を入力してください</t>
+          <t>直腸温</t>
         </is>
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>약품명을 입력해주세요</t>
+          <t>직장 온도</t>
         </is>
       </c>
       <c r="G373" s="4" t="n"/>
@@ -20655,32 +20655,32 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>medicine_dosage</t>
+          <t>medicine_name</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>剂量</t>
+          <t>药品名称</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Dosage</t>
+          <t>Drug name</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>劑量</t>
+          <t>藥品名稱</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
         <is>
-          <t>用量</t>
+          <t>薬剤名</t>
         </is>
       </c>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>용량</t>
+          <t>약명</t>
         </is>
       </c>
       <c r="G374" s="4" t="n"/>
@@ -20709,32 +20709,32 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>medicine_unit</t>
+          <t>medicine_name_hint</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>单位</t>
+          <t>请输入药品名称</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Please enter the drug name</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>請輸入藥品名稱</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
         <is>
-          <t>単位</t>
+          <t>薬剤名を入力してください</t>
         </is>
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>약품명을 입력해주세요</t>
         </is>
       </c>
       <c r="G375" s="4" t="n"/>
@@ -20763,32 +20763,32 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>vaccine_name</t>
+          <t>medicine_dosage</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>疫苗名称</t>
+          <t>剂量</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Vaccine name</t>
+          <t>Dosage</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>疫苗名稱</t>
+          <t>劑量</t>
         </is>
       </c>
       <c r="E376" s="4" t="inlineStr">
         <is>
-          <t>ワクチン名</t>
+          <t>用量</t>
         </is>
       </c>
       <c r="F376" s="4" t="inlineStr">
         <is>
-          <t>백신명</t>
+          <t>용량</t>
         </is>
       </c>
       <c r="G376" s="4" t="n"/>
@@ -20817,32 +20817,32 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>vaccine_name_hint</t>
+          <t>medicine_unit</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>请输入疫苗名称</t>
+          <t>单位</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Please enter vaccine name</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>請輸入疫苗名稱</t>
+          <t>單位</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
         <is>
-          <t>ワクチン名を入力してください</t>
+          <t>単位</t>
         </is>
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>백신 이름을 입력하세요.</t>
+          <t>단위</t>
         </is>
       </c>
       <c r="G377" s="4" t="n"/>
@@ -20871,32 +20871,32 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>vaccine_dose</t>
+          <t>vaccine_name</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>剂次</t>
+          <t>疫苗名称</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Vaccine name</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>劑次</t>
+          <t>疫苗名稱</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr">
         <is>
-          <t>回数</t>
+          <t>ワクチン名</t>
         </is>
       </c>
       <c r="F378" s="4" t="inlineStr">
         <is>
-          <t>차수</t>
+          <t>백신명</t>
         </is>
       </c>
       <c r="G378" s="4" t="n"/>
@@ -20925,32 +20925,32 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>vaccine_dose_hint</t>
+          <t>vaccine_name_hint</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>请输入剂次</t>
+          <t>请输入疫苗名称</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Enter dose</t>
+          <t>Please enter vaccine name</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>請輸入劑次</t>
+          <t>請輸入疫苗名稱</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
-          <t>投与回数を入力してください</t>
+          <t>ワクチン名を入力してください</t>
         </is>
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>투여횟수를 입력해 주세요</t>
+          <t>백신 이름을 입력하세요.</t>
         </is>
       </c>
       <c r="G379" s="4" t="n"/>
@@ -20979,32 +20979,32 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>vaccine_dose_format</t>
+          <t>vaccine_dose</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>第%1$d剂</t>
+          <t>剂次</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Dose %1$d</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>第%1$d劑</t>
+          <t>劑次</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr">
         <is>
-          <t>%1$d回目</t>
+          <t>回数</t>
         </is>
       </c>
       <c r="F380" s="4" t="inlineStr">
         <is>
-          <t>%1$d차</t>
+          <t>차수</t>
         </is>
       </c>
       <c r="G380" s="4" t="n"/>
@@ -21033,32 +21033,32 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>vaccine_site</t>
+          <t>vaccine_dose_hint</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>接种部位</t>
+          <t>请输入剂次</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Injection site</t>
+          <t>Enter dose</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>接種部位</t>
+          <t>請輸入劑次</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
-          <t>接種部位</t>
+          <t>投与回数を入力してください</t>
         </is>
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>접종 부위</t>
+          <t>투여횟수를 입력해 주세요</t>
         </is>
       </c>
       <c r="G381" s="4" t="n"/>
@@ -21087,32 +21087,32 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>vaccine_site_hint</t>
+          <t>vaccine_dose_format</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>如：左上臂</t>
+          <t>第%1$d剂</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>e.g. left arm</t>
+          <t>Dose %1$d</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>如：左上臂</t>
+          <t>第%1$d劑</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr">
         <is>
-          <t>例：左上腕</t>
+          <t>%1$d回目</t>
         </is>
       </c>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>예: 왼쪽 팔뚝</t>
+          <t>%1$d차</t>
         </is>
       </c>
       <c r="G382" s="4" t="n"/>
@@ -21141,32 +21141,32 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>vaccine_clinic</t>
+          <t>vaccine_site</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>接种机构</t>
+          <t>接种部位</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Injection site</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>接種機構</t>
+          <t>接種部位</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
-          <t>ワクチン接種機関</t>
+          <t>接種部位</t>
         </is>
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>예방접종 기관</t>
+          <t>접종 부위</t>
         </is>
       </c>
       <c r="G383" s="4" t="n"/>
@@ -21195,32 +21195,32 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>vaccine_clinic_hint</t>
+          <t>vaccine_site_hint</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>请输入接种机构</t>
+          <t>如：左上臂</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Enter clinic</t>
+          <t>e.g. left arm</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>請輸入接種機構</t>
+          <t>如：左上臂</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr">
         <is>
-          <t>予防接種機関を入力してください</t>
+          <t>例：左上腕</t>
         </is>
       </c>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>예방접종 기관을 입력해주세요.</t>
+          <t>예: 왼쪽 팔뚝</t>
         </is>
       </c>
       <c r="G384" s="4" t="n"/>
@@ -21249,32 +21249,32 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>vaccine_batch</t>
+          <t>vaccine_clinic</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>疫苗批号</t>
+          <t>接种机构</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Batch No.</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>疫苗批號</t>
+          <t>接種機構</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
         <is>
-          <t>ワクチンのバッチ番号</t>
+          <t>ワクチン接種機関</t>
         </is>
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>백신 배치 번호</t>
+          <t>예방접종 기관</t>
         </is>
       </c>
       <c r="G385" s="4" t="n"/>
@@ -21303,32 +21303,32 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>vaccine_batch_hint</t>
+          <t>vaccine_clinic_hint</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>请输入疫苗批号</t>
+          <t>请输入接种机构</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Enter batch number</t>
+          <t>Enter clinic</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
         <is>
-          <t>請輸入疫苗批號</t>
+          <t>請輸入接種機構</t>
         </is>
       </c>
       <c r="E386" s="4" t="inlineStr">
         <is>
-          <t>ワクチンのバッチ番号を入力してください</t>
+          <t>予防接種機関を入力してください</t>
         </is>
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>백신 배치 번호를 입력하세요.</t>
+          <t>예방접종 기관을 입력해주세요.</t>
         </is>
       </c>
       <c r="G386" s="4" t="n"/>
@@ -21357,32 +21357,32 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>symptom_description</t>
+          <t>vaccine_batch</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>症状描述</t>
+          <t>疫苗批号</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Symptom description</t>
+          <t>Batch No.</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
         <is>
-          <t>症狀描述</t>
+          <t>疫苗批號</t>
         </is>
       </c>
       <c r="E387" s="4" t="inlineStr">
         <is>
-          <t>症状の説明</t>
+          <t>ワクチンのバッチ番号</t>
         </is>
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>증상 설명</t>
+          <t>백신 배치 번호</t>
         </is>
       </c>
       <c r="G387" s="4" t="n"/>
@@ -21411,32 +21411,32 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>symptom_hint</t>
+          <t>vaccine_batch_hint</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>请描述症状</t>
+          <t>请输入疫苗批号</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Please describe symptoms</t>
+          <t>Enter batch number</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
         <is>
-          <t>請描述症狀</t>
+          <t>請輸入疫苗批號</t>
         </is>
       </c>
       <c r="E388" s="4" t="inlineStr">
         <is>
-          <t>症状を説明してください</t>
+          <t>ワクチンのバッチ番号を入力してください</t>
         </is>
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>증상을 설명해 주세요</t>
+          <t>백신 배치 번호를 입력하세요.</t>
         </is>
       </c>
       <c r="G388" s="4" t="n"/>
@@ -21465,32 +21465,32 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>event_growth_weight</t>
+          <t>symptom_description</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>体重</t>
+          <t>症状描述</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Symptom description</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
         <is>
-          <t>體重</t>
+          <t>症狀描述</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
-          <t>体重</t>
+          <t>症状の説明</t>
         </is>
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>체중</t>
+          <t>증상 설명</t>
         </is>
       </c>
       <c r="G389" s="4" t="n"/>
@@ -21519,32 +21519,32 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>event_growth_height</t>
+          <t>symptom_hint</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>身高</t>
+          <t>请描述症状</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Please describe symptoms</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>身高</t>
+          <t>請描述症狀</t>
         </is>
       </c>
       <c r="E390" s="4" t="inlineStr">
         <is>
-          <t>身長</t>
+          <t>症状を説明してください</t>
         </is>
       </c>
       <c r="F390" s="4" t="inlineStr">
         <is>
-          <t>키</t>
+          <t>증상을 설명해 주세요</t>
         </is>
       </c>
       <c r="G390" s="4" t="n"/>
@@ -21573,32 +21573,32 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>event_growth_head</t>
+          <t>event_growth_weight</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>头围</t>
+          <t>体重</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Head circumference</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>頭圍</t>
+          <t>體重</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>頭囲</t>
+          <t>体重</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>머리 둘레</t>
+          <t>체중</t>
         </is>
       </c>
       <c r="G391" s="4" t="n"/>
@@ -21627,32 +21627,32 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>weight_unit</t>
+          <t>event_growth_height</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>身高</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>身高</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>身長</t>
         </is>
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>키</t>
         </is>
       </c>
       <c r="G392" s="4" t="n"/>
@@ -21681,32 +21681,32 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>height_unit</t>
+          <t>event_growth_head</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>头围</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>Head circumference</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>頭圍</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>頭囲</t>
         </is>
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>머리 둘레</t>
         </is>
       </c>
       <c r="G393" s="4" t="n"/>
@@ -21735,32 +21735,32 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>last_record</t>
+          <t>weight_unit</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>上次记录</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>last record</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
         <is>
-          <t>上次記錄</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E394" s="4" t="inlineStr">
         <is>
-          <t>最後の記録</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F394" s="4" t="inlineStr">
         <is>
-          <t>마지막 기록</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G394" s="4" t="n"/>
@@ -21789,32 +21789,32 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>growth_change</t>
+          <t>height_unit</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>变化</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Change</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
         <is>
-          <t>變化</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>変化</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="G395" s="4" t="n"/>
@@ -21843,32 +21843,32 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_roll</t>
+          <t>last_record</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>翻身</t>
+          <t>上次记录</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Roll over</t>
+          <t>last record</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
         <is>
-          <t>翻身</t>
+          <t>上次記錄</t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr">
         <is>
-          <t>寝返り</t>
+          <t>最後の記録</t>
         </is>
       </c>
       <c r="F396" s="4" t="inlineStr">
         <is>
-          <t>뒤집기</t>
+          <t>마지막 기록</t>
         </is>
       </c>
       <c r="G396" s="4" t="n"/>
@@ -21897,32 +21897,32 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_sit</t>
+          <t>growth_change</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>独坐</t>
+          <t>变化</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Sit independently</t>
+          <t>Change</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
         <is>
-          <t>獨坐</t>
+          <t>變化</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
-          <t>ひとり座り</t>
+          <t>変化</t>
         </is>
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>혼자 앉기</t>
+          <t>변화</t>
         </is>
       </c>
       <c r="G397" s="4" t="n"/>
@@ -21951,32 +21951,32 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_crawl</t>
+          <t>event_milestone_roll</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>爬行</t>
+          <t>翻身</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Crawl</t>
+          <t>Roll over</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
         <is>
-          <t>爬行</t>
+          <t>翻身</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr">
         <is>
-          <t>はいはい</t>
+          <t>寝返り</t>
         </is>
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>뒤집기</t>
         </is>
       </c>
       <c r="G398" s="4" t="n"/>
@@ -22005,32 +22005,32 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_stand</t>
+          <t>event_milestone_sit</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>站立</t>
+          <t>独坐</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Stand</t>
+          <t>Sit independently</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
         <is>
-          <t>站立</t>
+          <t>獨坐</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
-          <t>立つ</t>
+          <t>ひとり座り</t>
         </is>
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>서기</t>
+          <t>혼자 앉기</t>
         </is>
       </c>
       <c r="G399" s="4" t="n"/>
@@ -22059,32 +22059,32 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_walk</t>
+          <t>event_milestone_crawl</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>行走</t>
+          <t>爬行</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Crawl</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
         <is>
-          <t>行走</t>
+          <t>爬行</t>
         </is>
       </c>
       <c r="E400" s="4" t="inlineStr">
         <is>
-          <t>歩く</t>
+          <t>はいはい</t>
         </is>
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>걷기</t>
+          <t>기기</t>
         </is>
       </c>
       <c r="G400" s="4" t="n"/>
@@ -22113,32 +22113,32 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_first_word</t>
+          <t>event_milestone_stand</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>第一个词</t>
+          <t>站立</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>first word</t>
+          <t>Stand</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
         <is>
-          <t>第一個字</t>
+          <t>站立</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
-          <t>最初の言葉</t>
+          <t>立つ</t>
         </is>
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>첫 번째 단어</t>
+          <t>서기</t>
         </is>
       </c>
       <c r="G401" s="4" t="n"/>
@@ -22167,32 +22167,32 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_first_tooth</t>
+          <t>event_milestone_walk</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>第一颗牙</t>
+          <t>行走</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>first tooth</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
         <is>
-          <t>第一顆牙</t>
+          <t>行走</t>
         </is>
       </c>
       <c r="E402" s="4" t="inlineStr">
         <is>
-          <t>最初の歯</t>
+          <t>歩く</t>
         </is>
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>첫 번째 치아</t>
+          <t>걷기</t>
         </is>
       </c>
       <c r="G402" s="4" t="n"/>
@@ -22221,32 +22221,32 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>event_milestone_custom</t>
+          <t>event_milestone_first_word</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>自定义</t>
+          <t>第一个词</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Customize</t>
+          <t>first word</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
         <is>
-          <t>自訂</t>
+          <t>第一個字</t>
         </is>
       </c>
       <c r="E403" s="4" t="inlineStr">
         <is>
-          <t>カスタマイズ</t>
+          <t>最初の言葉</t>
         </is>
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>사용자 정의</t>
+          <t>첫 번째 단어</t>
         </is>
       </c>
       <c r="G403" s="4" t="n"/>
@@ -22275,32 +22275,32 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>milestone_congratulation</t>
+          <t>event_milestone_first_tooth</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>🎉 恭喜！宝宝又进步了！</t>
+          <t>第一颗牙</t>
         </is>
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>🎉 Congratulations! The baby is making progress again!</t>
+          <t>first tooth</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
         <is>
-          <t>🎉 恭喜！寶寶又進步了！</t>
+          <t>第一顆牙</t>
         </is>
       </c>
       <c r="E404" s="4" t="inlineStr">
         <is>
-          <t>🎉 おめでとうございます！赤ちゃんはまた進歩しています！</t>
+          <t>最初の歯</t>
         </is>
       </c>
       <c r="F404" s="4" t="inlineStr">
         <is>
-          <t>🎉 축하합니다! 아기가 다시 발전하고 있어요!</t>
+          <t>첫 번째 치아</t>
         </is>
       </c>
       <c r="G404" s="4" t="n"/>
@@ -22329,32 +22329,32 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>milestone_name</t>
+          <t>event_milestone_custom</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>里程碑名称</t>
+          <t>自定义</t>
         </is>
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Milestone name</t>
+          <t>Customize</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
         <is>
-          <t>里程碑名稱</t>
+          <t>自訂</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr">
         <is>
-          <t>マイルストーン名</t>
+          <t>カスタマイズ</t>
         </is>
       </c>
       <c r="F405" s="4" t="inlineStr">
         <is>
-          <t>마일스톤 이름</t>
+          <t>사용자 정의</t>
         </is>
       </c>
       <c r="G405" s="4" t="n"/>
@@ -22383,32 +22383,32 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>milestone_name_hint</t>
+          <t>milestone_congratulation</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>请输入里程碑名称</t>
+          <t>🎉 恭喜！宝宝又进步了！</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Please enter a milestone name</t>
+          <t>🎉 Congratulations! The baby is making progress again!</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
         <is>
-          <t>請輸入里程碑名稱</t>
+          <t>🎉 恭喜！寶寶又進步了！</t>
         </is>
       </c>
       <c r="E406" s="4" t="inlineStr">
         <is>
-          <t>マイルストーン名を入力してください</t>
+          <t>🎉 おめでとうございます！赤ちゃんはまた進歩しています！</t>
         </is>
       </c>
       <c r="F406" s="4" t="inlineStr">
         <is>
-          <t>마일스톤 이름을 입력하세요.</t>
+          <t>🎉 축하합니다! 아기가 다시 발전하고 있어요!</t>
         </is>
       </c>
       <c r="G406" s="4" t="n"/>
@@ -22437,32 +22437,32 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>milestone_description</t>
+          <t>milestone_name</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>记录这个珍贵时刻</t>
+          <t>里程碑名称</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>record this precious moment</t>
+          <t>Milestone name</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>記錄這個珍貴時刻</t>
+          <t>里程碑名稱</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr">
         <is>
-          <t>この貴重な瞬間を記録します</t>
+          <t>マイルストーン名</t>
         </is>
       </c>
       <c r="F407" s="4" t="inlineStr">
         <is>
-          <t>이 소중한 순간을 기록해 보세요</t>
+          <t>마일스톤 이름</t>
         </is>
       </c>
       <c r="G407" s="4" t="n"/>
@@ -22491,32 +22491,32 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>milestone_description_hint</t>
+          <t>milestone_name_hint</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>今天宝宝…</t>
+          <t>请输入里程碑名称</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Today baby...</t>
+          <t>Please enter a milestone name</t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
         <is>
-          <t>今天寶寶…</t>
+          <t>請輸入里程碑名稱</t>
         </is>
       </c>
       <c r="E408" s="4" t="inlineStr">
         <is>
-          <t>今日、赤ちゃんは…</t>
+          <t>マイルストーン名を入力してください</t>
         </is>
       </c>
       <c r="F408" s="4" t="inlineStr">
         <is>
-          <t>오늘 아기는…</t>
+          <t>마일스톤 이름을 입력하세요.</t>
         </is>
       </c>
       <c r="G408" s="4" t="n"/>
@@ -22545,32 +22545,32 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>event_care_bath</t>
+          <t>milestone_description</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>洗澡</t>
+          <t>记录这个珍贵时刻</t>
         </is>
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>record this precious moment</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>洗澡</t>
+          <t>記錄這個珍貴時刻</t>
         </is>
       </c>
       <c r="E409" s="4" t="inlineStr">
         <is>
-          <t>入浴</t>
+          <t>この貴重な瞬間を記録します</t>
         </is>
       </c>
       <c r="F409" s="4" t="inlineStr">
         <is>
-          <t>목욕</t>
+          <t>이 소중한 순간을 기록해 보세요</t>
         </is>
       </c>
       <c r="G409" s="4" t="n"/>
@@ -22599,32 +22599,32 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>event_care_nail</t>
+          <t>milestone_description_hint</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>剪指甲</t>
+          <t>今天宝宝…</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Trim nails</t>
+          <t>Today baby...</t>
         </is>
       </c>
       <c r="D410" s="4" t="inlineStr">
         <is>
-          <t>剪指甲</t>
+          <t>今天寶寶…</t>
         </is>
       </c>
       <c r="E410" s="4" t="inlineStr">
         <is>
-          <t>爪切り</t>
+          <t>今日、赤ちゃんは…</t>
         </is>
       </c>
       <c r="F410" s="4" t="inlineStr">
         <is>
-          <t>손톱 깎기</t>
+          <t>오늘 아기는…</t>
         </is>
       </c>
       <c r="G410" s="4" t="n"/>
@@ -22653,32 +22653,32 @@
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>event_care_skincare</t>
+          <t>event_care_bath</t>
         </is>
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>护肤</t>
+          <t>洗澡</t>
         </is>
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Skin care</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>保養</t>
+          <t>洗澡</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr">
         <is>
-          <t>スキンケア</t>
+          <t>入浴</t>
         </is>
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>스킨 케어</t>
+          <t>목욕</t>
         </is>
       </c>
       <c r="G411" s="4" t="n"/>
@@ -22707,32 +22707,32 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>event_care_massage</t>
+          <t>event_care_nail</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>抚触按摩</t>
+          <t>剪指甲</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Baby massage</t>
+          <t>Trim nails</t>
         </is>
       </c>
       <c r="D412" s="4" t="inlineStr">
         <is>
-          <t>撫觸按摩</t>
+          <t>剪指甲</t>
         </is>
       </c>
       <c r="E412" s="4" t="inlineStr">
         <is>
-          <t>ベビーマッサージ</t>
+          <t>爪切り</t>
         </is>
       </c>
       <c r="F412" s="4" t="inlineStr">
         <is>
-          <t>베이비 마사지</t>
+          <t>손톱 깎기</t>
         </is>
       </c>
       <c r="G412" s="4" t="n"/>
@@ -22761,32 +22761,32 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>event_care_nose</t>
+          <t>event_care_skincare</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>清洁鼻腔</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Clean nasal cavity</t>
+          <t>Skin care</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
         <is>
-          <t>清潔鼻腔</t>
+          <t>保養</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr">
         <is>
-          <t>鼻腔をきれいにする</t>
+          <t>スキンケア</t>
         </is>
       </c>
       <c r="F413" s="4" t="inlineStr">
         <is>
-          <t>깨끗한 비강</t>
+          <t>스킨 케어</t>
         </is>
       </c>
       <c r="G413" s="4" t="n"/>
@@ -22815,32 +22815,32 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>event_care_ear</t>
+          <t>event_care_massage</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>清洁耳朵</t>
+          <t>抚触按摩</t>
         </is>
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>clean ears</t>
+          <t>Baby massage</t>
         </is>
       </c>
       <c r="D414" s="4" t="inlineStr">
         <is>
-          <t>清潔耳朵</t>
+          <t>撫觸按摩</t>
         </is>
       </c>
       <c r="E414" s="4" t="inlineStr">
         <is>
-          <t>耳をきれいにする</t>
+          <t>ベビーマッサージ</t>
         </is>
       </c>
       <c r="F414" s="4" t="inlineStr">
         <is>
-          <t>깨끗한 귀</t>
+          <t>베이비 마사지</t>
         </is>
       </c>
       <c r="G414" s="4" t="n"/>
@@ -22869,32 +22869,32 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>event_activity_outdoor</t>
+          <t>event_care_nose</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>户外活动</t>
+          <t>清洁鼻腔</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>outdoor activities</t>
+          <t>Clean nasal cavity</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
         <is>
-          <t>戶外活動</t>
+          <t>清潔鼻腔</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr">
         <is>
-          <t>アウトドアアクティビティ</t>
+          <t>鼻腔をきれいにする</t>
         </is>
       </c>
       <c r="F415" s="4" t="inlineStr">
         <is>
-          <t>야외 활동</t>
+          <t>깨끗한 비강</t>
         </is>
       </c>
       <c r="G415" s="4" t="n"/>
@@ -22923,32 +22923,32 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>event_activity_tummy</t>
+          <t>event_care_ear</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>趴趴时间</t>
+          <t>清洁耳朵</t>
         </is>
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Tummy time</t>
+          <t>clean ears</t>
         </is>
       </c>
       <c r="D416" s="4" t="inlineStr">
         <is>
-          <t>趴趴時間</t>
+          <t>清潔耳朵</t>
         </is>
       </c>
       <c r="E416" s="4" t="inlineStr">
         <is>
-          <t>うつぶせ遊び</t>
+          <t>耳をきれいにする</t>
         </is>
       </c>
       <c r="F416" s="4" t="inlineStr">
         <is>
-          <t>터미 타임</t>
+          <t>깨끗한 귀</t>
         </is>
       </c>
       <c r="G416" s="4" t="n"/>
@@ -22977,32 +22977,32 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>event_activity_swimming</t>
+          <t>event_activity_outdoor</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>游泳</t>
+          <t>户外活动</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>swim</t>
+          <t>outdoor activities</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>游泳</t>
+          <t>戶外活動</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr">
         <is>
-          <t>水泳</t>
+          <t>アウトドアアクティビティ</t>
         </is>
       </c>
       <c r="F417" s="4" t="inlineStr">
         <is>
-          <t>수영</t>
+          <t>야외 활동</t>
         </is>
       </c>
       <c r="G417" s="4" t="n"/>
@@ -23031,32 +23031,32 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>event_activity_play</t>
+          <t>event_activity_tummy</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>亲子游戏</t>
+          <t>趴趴时间</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Parent-child play</t>
+          <t>Tummy time</t>
         </is>
       </c>
       <c r="D418" s="4" t="inlineStr">
         <is>
-          <t>親子遊戲</t>
+          <t>趴趴時間</t>
         </is>
       </c>
       <c r="E418" s="4" t="inlineStr">
         <is>
-          <t>親子遊び</t>
+          <t>うつぶせ遊び</t>
         </is>
       </c>
       <c r="F418" s="4" t="inlineStr">
         <is>
-          <t>부모-아이 놀이</t>
+          <t>터미 타임</t>
         </is>
       </c>
       <c r="G418" s="4" t="n"/>
@@ -23085,32 +23085,32 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>use_timer</t>
+          <t>event_activity_swimming</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>使用计时器</t>
+          <t>游泳</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Use a timer</t>
+          <t>swim</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>使用計時器</t>
+          <t>游泳</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr">
         <is>
-          <t>タイマーを使用する</t>
+          <t>水泳</t>
         </is>
       </c>
       <c r="F419" s="4" t="inlineStr">
         <is>
-          <t>타이머를 사용하세요</t>
+          <t>수영</t>
         </is>
       </c>
       <c r="G419" s="4" t="n"/>
@@ -23139,32 +23139,32 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>event_other_burp</t>
+          <t>event_activity_play</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>拍嗝</t>
+          <t>亲子游戏</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>burp</t>
+          <t>Parent-child play</t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
         <is>
-          <t>拍嗝</t>
+          <t>親子遊戲</t>
         </is>
       </c>
       <c r="E420" s="4" t="inlineStr">
         <is>
-          <t>ゲップ</t>
+          <t>親子遊び</t>
         </is>
       </c>
       <c r="F420" s="4" t="inlineStr">
         <is>
-          <t>트림</t>
+          <t>부모-아이 놀이</t>
         </is>
       </c>
       <c r="G420" s="4" t="n"/>
@@ -23193,32 +23193,32 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>event_other_cry</t>
+          <t>use_timer</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>哭闹</t>
+          <t>使用计时器</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>crying</t>
+          <t>Use a timer</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>哭鬧</t>
+          <t>使用計時器</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr">
         <is>
-          <t>泣いている</t>
+          <t>タイマーを使用する</t>
         </is>
       </c>
       <c r="F421" s="4" t="inlineStr">
         <is>
-          <t>울고</t>
+          <t>타이머를 사용하세요</t>
         </is>
       </c>
       <c r="G421" s="4" t="n"/>
@@ -23247,32 +23247,32 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>event_other_spit_up</t>
+          <t>event_other_burp</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>吐奶</t>
+          <t>拍嗝</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Spit-up</t>
+          <t>burp</t>
         </is>
       </c>
       <c r="D422" s="4" t="inlineStr">
         <is>
-          <t>吐奶</t>
+          <t>拍嗝</t>
         </is>
       </c>
       <c r="E422" s="4" t="inlineStr">
         <is>
-          <t>吐き戻し</t>
+          <t>ゲップ</t>
         </is>
       </c>
       <c r="F422" s="4" t="inlineStr">
         <is>
-          <t>토함</t>
+          <t>트림</t>
         </is>
       </c>
       <c r="G422" s="4" t="n"/>
@@ -23301,32 +23301,32 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>event_other_custom</t>
+          <t>event_other_cry</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>自定义</t>
+          <t>哭闹</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Customize</t>
+          <t>crying</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>自訂</t>
+          <t>哭鬧</t>
         </is>
       </c>
       <c r="E423" s="4" t="inlineStr">
         <is>
-          <t>カスタマイズ</t>
+          <t>泣いている</t>
         </is>
       </c>
       <c r="F423" s="4" t="inlineStr">
         <is>
-          <t>사용자 정의</t>
+          <t>울고</t>
         </is>
       </c>
       <c r="G423" s="4" t="n"/>
@@ -23355,32 +23355,32 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>custom_event_name</t>
+          <t>event_other_spit_up</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>事件名称</t>
+          <t>吐奶</t>
         </is>
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Event name</t>
+          <t>Spit-up</t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
         <is>
-          <t>事件名稱</t>
+          <t>吐奶</t>
         </is>
       </c>
       <c r="E424" s="4" t="inlineStr">
         <is>
-          <t>イベント名</t>
+          <t>吐き戻し</t>
         </is>
       </c>
       <c r="F424" s="4" t="inlineStr">
         <is>
-          <t>이벤트 이름</t>
+          <t>토함</t>
         </is>
       </c>
       <c r="G424" s="4" t="n"/>
@@ -23409,32 +23409,32 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>custom_event_hint</t>
+          <t>event_other_custom</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>请输入事件名称</t>
+          <t>自定义</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Please enter event name</t>
+          <t>Customize</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>請輸入事件名稱</t>
+          <t>自訂</t>
         </is>
       </c>
       <c r="E425" s="4" t="inlineStr">
         <is>
-          <t>イベント名を入力してください</t>
+          <t>カスタマイズ</t>
         </is>
       </c>
       <c r="F425" s="4" t="inlineStr">
         <is>
-          <t>이벤트 이름을 입력해주세요</t>
+          <t>사용자 정의</t>
         </is>
       </c>
       <c r="G425" s="4" t="n"/>
@@ -23463,32 +23463,32 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>custom_event_description</t>
+          <t>custom_event_name</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>事件描述</t>
+          <t>事件名称</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Event name</t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
         <is>
-          <t>事件描述</t>
+          <t>事件名稱</t>
         </is>
       </c>
       <c r="E426" s="4" t="inlineStr">
         <is>
-          <t>イベントの説明</t>
+          <t>イベント名</t>
         </is>
       </c>
       <c r="F426" s="4" t="inlineStr">
         <is>
-          <t>이벤트 설명</t>
+          <t>이벤트 이름</t>
         </is>
       </c>
       <c r="G426" s="4" t="n"/>
@@ -23517,32 +23517,32 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>custom_event_description_hint</t>
+          <t>custom_event_hint</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>请输入事件描述</t>
+          <t>请输入事件名称</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Enter description</t>
+          <t>Please enter event name</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>請輸入事件描述</t>
+          <t>請輸入事件名稱</t>
         </is>
       </c>
       <c r="E427" s="4" t="inlineStr">
         <is>
-          <t>イベントの説明を入力してください</t>
+          <t>イベント名を入力してください</t>
         </is>
       </c>
       <c r="F427" s="4" t="inlineStr">
         <is>
-          <t>이벤트 설명을 입력하세요.</t>
+          <t>이벤트 이름을 입력해주세요</t>
         </is>
       </c>
       <c r="G427" s="4" t="n"/>
@@ -23571,32 +23571,32 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>custom_event_required</t>
+          <t>custom_event_description</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>请输入事件名称或描述</t>
+          <t>事件描述</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Enter a name or description</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D428" s="4" t="inlineStr">
         <is>
-          <t>請輸入事件名稱或描述</t>
+          <t>事件描述</t>
         </is>
       </c>
       <c r="E428" s="4" t="inlineStr">
         <is>
-          <t>イベント名または説明を入力してください</t>
+          <t>イベントの説明</t>
         </is>
       </c>
       <c r="F428" s="4" t="inlineStr">
         <is>
-          <t>이벤트 이름이나 설명을 입력하세요.</t>
+          <t>이벤트 설명</t>
         </is>
       </c>
       <c r="G428" s="4" t="n"/>
@@ -23625,32 +23625,32 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>statistics</t>
+          <t>custom_event_description_hint</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>统计</t>
+          <t>请输入事件描述</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Enter description</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
         <is>
-          <t>統計</t>
+          <t>請輸入事件描述</t>
         </is>
       </c>
       <c r="E429" s="4" t="inlineStr">
         <is>
-          <t>統計</t>
+          <t>イベントの説明を入力してください</t>
         </is>
       </c>
       <c r="F429" s="4" t="inlineStr">
         <is>
-          <t>통계</t>
+          <t>이벤트 설명을 입력하세요.</t>
         </is>
       </c>
       <c r="G429" s="4" t="n"/>
@@ -23679,32 +23679,32 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_title</t>
+          <t>custom_event_required</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>生长趋势</t>
+          <t>请输入事件名称或描述</t>
         </is>
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Growth trends</t>
+          <t>Enter a name or description</t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
         <is>
-          <t>生長趨勢</t>
+          <t>請輸入事件名稱或描述</t>
         </is>
       </c>
       <c r="E430" s="4" t="inlineStr">
         <is>
-          <t>成長傾向</t>
+          <t>イベント名または説明を入力してください</t>
         </is>
       </c>
       <c r="F430" s="4" t="inlineStr">
         <is>
-          <t>성장 추세</t>
+          <t>이벤트 이름이나 설명을 입력하세요.</t>
         </is>
       </c>
       <c r="G430" s="4" t="n"/>
@@ -23733,32 +23733,32 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_weight</t>
+          <t>statistics</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>体重</t>
+          <t>统计</t>
         </is>
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Statistics</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
         <is>
-          <t>體重</t>
+          <t>統計</t>
         </is>
       </c>
       <c r="E431" s="4" t="inlineStr">
         <is>
-          <t>重量</t>
+          <t>統計</t>
         </is>
       </c>
       <c r="F431" s="4" t="inlineStr">
         <is>
-          <t>무게</t>
+          <t>통계</t>
         </is>
       </c>
       <c r="G431" s="4" t="n"/>
@@ -23787,32 +23787,32 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_height</t>
+          <t>statistics_growth_title</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>身高</t>
+          <t>生长趋势</t>
         </is>
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Growth trends</t>
         </is>
       </c>
       <c r="D432" s="4" t="inlineStr">
         <is>
-          <t>身高</t>
+          <t>生長趨勢</t>
         </is>
       </c>
       <c r="E432" s="4" t="inlineStr">
         <is>
-          <t>身長</t>
+          <t>成長傾向</t>
         </is>
       </c>
       <c r="F432" s="4" t="inlineStr">
         <is>
-          <t>신장</t>
+          <t>성장 추세</t>
         </is>
       </c>
       <c r="G432" s="4" t="n"/>
@@ -23841,32 +23841,32 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_head</t>
+          <t>statistics_growth_weight</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>头围</t>
+          <t>体重</t>
         </is>
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
         <is>
-          <t>頭圍</t>
+          <t>體重</t>
         </is>
       </c>
       <c r="E433" s="4" t="inlineStr">
         <is>
-          <t>頭囲</t>
+          <t>重量</t>
         </is>
       </c>
       <c r="F433" s="4" t="inlineStr">
         <is>
-          <t>머리 둘레</t>
+          <t>무게</t>
         </is>
       </c>
       <c r="G433" s="4" t="n"/>
@@ -23895,32 +23895,32 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_no_record</t>
+          <t>statistics_growth_height</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>暂无记录</t>
+          <t>身高</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>No record</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D434" s="4" t="inlineStr">
         <is>
-          <t>暫無紀錄</t>
+          <t>身高</t>
         </is>
       </c>
       <c r="E434" s="4" t="inlineStr">
         <is>
-          <t>まだ記録がありません</t>
+          <t>身長</t>
         </is>
       </c>
       <c r="F434" s="4" t="inlineStr">
         <is>
-          <t>아직 기록이 없습니다</t>
+          <t>신장</t>
         </is>
       </c>
       <c r="G434" s="4" t="n"/>
@@ -23949,32 +23949,32 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_no_change</t>
+          <t>statistics_growth_head</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>较上次 无变化</t>
+          <t>头围</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>No change vs last</t>
+          <t>Head</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
         <is>
-          <t>較上次 無變化</t>
+          <t>頭圍</t>
         </is>
       </c>
       <c r="E435" s="4" t="inlineStr">
         <is>
-          <t>前回から変化なし</t>
+          <t>頭囲</t>
         </is>
       </c>
       <c r="F435" s="4" t="inlineStr">
         <is>
-          <t>지난번과 변함이 없네요</t>
+          <t>머리 둘레</t>
         </is>
       </c>
       <c r="G435" s="4" t="n"/>
@@ -24003,32 +24003,32 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_diff_format</t>
+          <t>statistics_growth_no_record</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>较上次 %1$s</t>
+          <t>暂无记录</t>
         </is>
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Vs last %1$s</t>
+          <t>No record</t>
         </is>
       </c>
       <c r="D436" s="4" t="inlineStr">
         <is>
-          <t>較上次 %1$s</t>
+          <t>暫無紀錄</t>
         </is>
       </c>
       <c r="E436" s="4" t="inlineStr">
         <is>
-          <t>前回との比較 %1$s</t>
+          <t>まだ記録がありません</t>
         </is>
       </c>
       <c r="F436" s="4" t="inlineStr">
         <is>
-          <t>지난번과 비교하면 %1$s</t>
+          <t>아직 기록이 없습니다</t>
         </is>
       </c>
       <c r="G436" s="4" t="n"/>
@@ -24057,32 +24057,32 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_placeholder</t>
+          <t>statistics_growth_no_change</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>较上次 无变化</t>
         </is>
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>No change vs last</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>較上次 無變化</t>
         </is>
       </c>
       <c r="E437" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>前回から変化なし</t>
         </is>
       </c>
       <c r="F437" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>지난번과 변함이 없네요</t>
         </is>
       </c>
       <c r="G437" s="4" t="n"/>
@@ -24111,32 +24111,32 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>statistics_value_with_unit_format</t>
+          <t>statistics_growth_diff_format</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>%1$s%2$s</t>
+          <t>较上次 %1$s</t>
         </is>
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>%1$s%2$s</t>
+          <t>Vs last %1$s</t>
         </is>
       </c>
       <c r="D438" s="4" t="inlineStr">
         <is>
-          <t>%1$s%2$s</t>
+          <t>較上次 %1$s</t>
         </is>
       </c>
       <c r="E438" s="4" t="inlineStr">
         <is>
-          <t>%1$s%2$s</t>
+          <t>前回との比較 %1$s</t>
         </is>
       </c>
       <c r="F438" s="4" t="inlineStr">
         <is>
-          <t>%1$s%2$s</t>
+          <t>지난번과 비교하면 %1$s</t>
         </is>
       </c>
       <c r="G438" s="4" t="n"/>
@@ -24165,32 +24165,32 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_title</t>
+          <t>statistics_growth_placeholder</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>趋势概览</t>
+          <t>--</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Trend overview</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
         <is>
-          <t>趨勢概覽</t>
+          <t>--</t>
         </is>
       </c>
       <c r="E439" s="4" t="inlineStr">
         <is>
-          <t>トレンドの概要</t>
+          <t>--</t>
         </is>
       </c>
       <c r="F439" s="4" t="inlineStr">
         <is>
-          <t>트렌드 개요</t>
+          <t>--</t>
         </is>
       </c>
       <c r="G439" s="4" t="n"/>
@@ -24219,32 +24219,32 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_week</t>
+          <t>statistics_value_with_unit_format</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>本周</t>
+          <t>%1$s%2$s</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>This week</t>
+          <t>%1$s%2$s</t>
         </is>
       </c>
       <c r="D440" s="4" t="inlineStr">
         <is>
-          <t>本週</t>
+          <t>%1$s%2$s</t>
         </is>
       </c>
       <c r="E440" s="4" t="inlineStr">
         <is>
-          <t>今週</t>
+          <t>%1$s%2$s</t>
         </is>
       </c>
       <c r="F440" s="4" t="inlineStr">
         <is>
-          <t>이번 주</t>
+          <t>%1$s%2$s</t>
         </is>
       </c>
       <c r="G440" s="4" t="n"/>
@@ -24273,32 +24273,32 @@
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_month</t>
+          <t>statistics_trend_title</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>本月</t>
+          <t>趋势概览</t>
         </is>
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>This month</t>
+          <t>Trend overview</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
         <is>
-          <t>本月</t>
+          <t>趨勢概覽</t>
         </is>
       </c>
       <c r="E441" s="4" t="inlineStr">
         <is>
-          <t>今月</t>
+          <t>トレンドの概要</t>
         </is>
       </c>
       <c r="F441" s="4" t="inlineStr">
         <is>
-          <t>이번 달</t>
+          <t>트렌드 개요</t>
         </is>
       </c>
       <c r="G441" s="4" t="n"/>
@@ -24327,32 +24327,32 @@
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_year</t>
+          <t>statistics_trend_week</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>本年</t>
+          <t>本周</t>
         </is>
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>This year</t>
+          <t>This week</t>
         </is>
       </c>
       <c r="D442" s="4" t="inlineStr">
         <is>
-          <t>本年</t>
+          <t>本週</t>
         </is>
       </c>
       <c r="E442" s="4" t="inlineStr">
         <is>
-          <t>今年は</t>
+          <t>今週</t>
         </is>
       </c>
       <c r="F442" s="4" t="inlineStr">
         <is>
-          <t>올해</t>
+          <t>이번 주</t>
         </is>
       </c>
       <c r="G442" s="4" t="n"/>
@@ -24381,32 +24381,32 @@
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_range_format</t>
+          <t>statistics_trend_month</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>%1$s-%2$s</t>
+          <t>本月</t>
         </is>
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>%1$s-%2$s</t>
+          <t>This month</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
         <is>
-          <t>%1$s-%2$s</t>
+          <t>本月</t>
         </is>
       </c>
       <c r="E443" s="4" t="inlineStr">
         <is>
-          <t>%1$s-%2$s</t>
+          <t>今月</t>
         </is>
       </c>
       <c r="F443" s="4" t="inlineStr">
         <is>
-          <t>%1$s-%2$s</t>
+          <t>이번 달</t>
         </is>
       </c>
       <c r="G443" s="4" t="n"/>
@@ -24435,32 +24435,32 @@
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_metric_feeding</t>
+          <t>statistics_trend_year</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>喂养</t>
+          <t>本年</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Feeding</t>
+          <t>This year</t>
         </is>
       </c>
       <c r="D444" s="4" t="inlineStr">
         <is>
-          <t>餵食</t>
+          <t>本年</t>
         </is>
       </c>
       <c r="E444" s="4" t="inlineStr">
         <is>
-          <t>授乳</t>
+          <t>今年は</t>
         </is>
       </c>
       <c r="F444" s="4" t="inlineStr">
         <is>
-          <t>수유</t>
+          <t>올해</t>
         </is>
       </c>
       <c r="G444" s="4" t="n"/>
@@ -24489,32 +24489,32 @@
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_metric_sleep</t>
+          <t>statistics_trend_range_format</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>睡眠</t>
+          <t>%1$s-%2$s</t>
         </is>
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Sleep</t>
+          <t>%1$s-%2$s</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
         <is>
-          <t>睡眠</t>
+          <t>%1$s-%2$s</t>
         </is>
       </c>
       <c r="E445" s="4" t="inlineStr">
         <is>
-          <t>睡眠</t>
+          <t>%1$s-%2$s</t>
         </is>
       </c>
       <c r="F445" s="4" t="inlineStr">
         <is>
-          <t>수면</t>
+          <t>%1$s-%2$s</t>
         </is>
       </c>
       <c r="G445" s="4" t="n"/>
@@ -24543,32 +24543,32 @@
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_metric_diaper</t>
+          <t>statistics_trend_metric_feeding</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>尿布</t>
+          <t>喂养</t>
         </is>
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Diaper</t>
+          <t>Feeding</t>
         </is>
       </c>
       <c r="D446" s="4" t="inlineStr">
         <is>
-          <t>尿布</t>
+          <t>餵食</t>
         </is>
       </c>
       <c r="E446" s="4" t="inlineStr">
         <is>
-          <t>おむつ</t>
+          <t>授乳</t>
         </is>
       </c>
       <c r="F446" s="4" t="inlineStr">
         <is>
-          <t>기저귀</t>
+          <t>수유</t>
         </is>
       </c>
       <c r="G446" s="4" t="n"/>
@@ -24597,32 +24597,32 @@
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_metric_event</t>
+          <t>statistics_trend_metric_sleep</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>其他事件</t>
+          <t>睡眠</t>
         </is>
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Other events</t>
+          <t>Sleep</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
         <is>
-          <t>其他事件</t>
+          <t>睡眠</t>
         </is>
       </c>
       <c r="E447" s="4" t="inlineStr">
         <is>
-          <t>その他のイベント</t>
+          <t>睡眠</t>
         </is>
       </c>
       <c r="F447" s="4" t="inlineStr">
         <is>
-          <t>기타 이벤트</t>
+          <t>수면</t>
         </is>
       </c>
       <c r="G447" s="4" t="n"/>
@@ -24651,32 +24651,32 @@
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_feeding_value_format</t>
+          <t>statistics_trend_metric_diaper</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>%1$d次 · %2$s</t>
+          <t>尿布</t>
         </is>
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>%1$d times / %2$s</t>
+          <t>Diaper</t>
         </is>
       </c>
       <c r="D448" s="4" t="inlineStr">
         <is>
-          <t>%1$d次 · %2$s</t>
+          <t>尿布</t>
         </is>
       </c>
       <c r="E448" s="4" t="inlineStr">
         <is>
-          <t>%1$d 回 · %2$s</t>
+          <t>おむつ</t>
         </is>
       </c>
       <c r="F448" s="4" t="inlineStr">
         <is>
-          <t>%1$d회 · %2$s</t>
+          <t>기저귀</t>
         </is>
       </c>
       <c r="G448" s="4" t="n"/>
@@ -24705,32 +24705,32 @@
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_sleep_value_format</t>
+          <t>statistics_trend_metric_event</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>%1$d次 · %2$s</t>
+          <t>其他事件</t>
         </is>
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>%1$d times / %2$s</t>
+          <t>Other events</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
         <is>
-          <t>%1$d次 · %2$s</t>
+          <t>其他事件</t>
         </is>
       </c>
       <c r="E449" s="4" t="inlineStr">
         <is>
-          <t>%1$d 回 · %2$s</t>
+          <t>その他のイベント</t>
         </is>
       </c>
       <c r="F449" s="4" t="inlineStr">
         <is>
-          <t>%1$d회 · %2$s</t>
+          <t>기타 이벤트</t>
         </is>
       </c>
       <c r="G449" s="4" t="n"/>
@@ -24759,32 +24759,32 @@
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_count_format</t>
+          <t>statistics_trend_feeding_value_format</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>%1$d次</t>
+          <t>%1$d次 · %2$s</t>
         </is>
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>%1$d times</t>
+          <t>%1$d times / %2$s</t>
         </is>
       </c>
       <c r="D450" s="4" t="inlineStr">
         <is>
-          <t>%1$d次</t>
+          <t>%1$d次 · %2$s</t>
         </is>
       </c>
       <c r="E450" s="4" t="inlineStr">
         <is>
-          <t>%1$d 回</t>
+          <t>%1$d 回 · %2$s</t>
         </is>
       </c>
       <c r="F450" s="4" t="inlineStr">
         <is>
-          <t>%1$d회</t>
+          <t>%1$d회 · %2$s</t>
         </is>
       </c>
       <c r="G450" s="4" t="n"/>
@@ -24813,32 +24813,32 @@
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>statistics_trend_placeholder</t>
+          <t>statistics_trend_sleep_value_format</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>%1$d次 · %2$s</t>
         </is>
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>%1$d times / %2$s</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>%1$d次 · %2$s</t>
         </is>
       </c>
       <c r="E451" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>%1$d 回 · %2$s</t>
         </is>
       </c>
       <c r="F451" s="4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>%1$d회 · %2$s</t>
         </is>
       </c>
       <c r="G451" s="4" t="n"/>
@@ -24867,32 +24867,32 @@
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>statistics_structure_title</t>
+          <t>statistics_trend_count_format</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>结构图</t>
+          <t>%1$d次</t>
         </is>
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>%1$d times</t>
         </is>
       </c>
       <c r="D452" s="4" t="inlineStr">
         <is>
-          <t>結構圖</t>
+          <t>%1$d次</t>
         </is>
       </c>
       <c r="E452" s="4" t="inlineStr">
         <is>
-          <t>構造図</t>
+          <t>%1$d 回</t>
         </is>
       </c>
       <c r="F452" s="4" t="inlineStr">
         <is>
-          <t>구조도</t>
+          <t>%1$d회</t>
         </is>
       </c>
       <c r="G452" s="4" t="n"/>
@@ -24921,32 +24921,32 @@
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>statistics_structure_feeding_title</t>
+          <t>statistics_trend_placeholder</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>喂养结构</t>
+          <t>--</t>
         </is>
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Feeding mix</t>
+          <t>--</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
         <is>
-          <t>餵食結構</t>
+          <t>--</t>
         </is>
       </c>
       <c r="E453" s="4" t="inlineStr">
         <is>
-          <t>授乳構成</t>
+          <t>--</t>
         </is>
       </c>
       <c r="F453" s="4" t="inlineStr">
         <is>
-          <t>수유 구성</t>
+          <t>--</t>
         </is>
       </c>
       <c r="G453" s="4" t="n"/>
@@ -24975,32 +24975,32 @@
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>statistics_structure_diaper_title</t>
+          <t>statistics_structure_title</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>排泄结构</t>
+          <t>结构图</t>
         </is>
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Diaper mix</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="D454" s="4" t="inlineStr">
         <is>
-          <t>排泄結構</t>
+          <t>結構圖</t>
         </is>
       </c>
       <c r="E454" s="4" t="inlineStr">
         <is>
-          <t>おむつ構成</t>
+          <t>構造図</t>
         </is>
       </c>
       <c r="F454" s="4" t="inlineStr">
         <is>
-          <t>기저귀 구성</t>
+          <t>구조도</t>
         </is>
       </c>
       <c r="G454" s="4" t="n"/>
@@ -25029,32 +25029,32 @@
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>statistics_structure_health_title</t>
+          <t>statistics_structure_feeding_title</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>健康结构</t>
+          <t>喂养结构</t>
         </is>
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Health mix</t>
+          <t>Feeding mix</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
-          <t>健康結構</t>
+          <t>餵食結構</t>
         </is>
       </c>
       <c r="E455" s="4" t="inlineStr">
         <is>
-          <t>健康構成</t>
+          <t>授乳構成</t>
         </is>
       </c>
       <c r="F455" s="4" t="inlineStr">
         <is>
-          <t>건강 구성</t>
+          <t>수유 구성</t>
         </is>
       </c>
       <c r="G455" s="4" t="n"/>
@@ -25083,32 +25083,32 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>statistics_structure_empty</t>
+          <t>statistics_structure_diaper_title</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>暂无结构数据</t>
+          <t>排泄结构</t>
         </is>
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>No structure data</t>
+          <t>Diaper mix</t>
         </is>
       </c>
       <c r="D456" s="4" t="inlineStr">
         <is>
-          <t>暫無結構數據</t>
+          <t>排泄結構</t>
         </is>
       </c>
       <c r="E456" s="4" t="inlineStr">
         <is>
-          <t>構造データはまだありません</t>
+          <t>おむつ構成</t>
         </is>
       </c>
       <c r="F456" s="4" t="inlineStr">
         <is>
-          <t>아직 구조 데이터가 없습니다.</t>
+          <t>기저귀 구성</t>
         </is>
       </c>
       <c r="G456" s="4" t="n"/>
@@ -25137,32 +25137,32 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>statistics_structure_legend_format</t>
+          <t>statistics_structure_health_title</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>%1$d次 · %2$d%%</t>
+          <t>健康结构</t>
         </is>
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>%1$d times / %2$d%%</t>
+          <t>Health mix</t>
         </is>
       </c>
       <c r="D457" s="4" t="inlineStr">
         <is>
-          <t>%1$d次 · %2$d%%</t>
+          <t>健康結構</t>
         </is>
       </c>
       <c r="E457" s="4" t="inlineStr">
         <is>
-          <t>%1$d 回 · %2$d%%</t>
+          <t>健康構成</t>
         </is>
       </c>
       <c r="F457" s="4" t="inlineStr">
         <is>
-          <t>%1$d회 · %2$d%%</t>
+          <t>건강 구성</t>
         </is>
       </c>
       <c r="G457" s="4" t="n"/>
@@ -25191,32 +25191,32 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_percentile_title</t>
+          <t>statistics_structure_empty</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>成长曲线百分位</t>
+          <t>暂无结构数据</t>
         </is>
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Growth percentiles</t>
+          <t>No structure data</t>
         </is>
       </c>
       <c r="D458" s="4" t="inlineStr">
         <is>
-          <t>成長曲線百分位</t>
+          <t>暫無結構數據</t>
         </is>
       </c>
       <c r="E458" s="4" t="inlineStr">
         <is>
-          <t>成長曲線のパーセンタイル</t>
+          <t>構造データはまだありません</t>
         </is>
       </c>
       <c r="F458" s="4" t="inlineStr">
         <is>
-          <t>성장 곡선 백분위수</t>
+          <t>아직 구조 데이터가 없습니다.</t>
         </is>
       </c>
       <c r="G458" s="4" t="n"/>
@@ -25245,32 +25245,32 @@
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_percentile_note</t>
+          <t>statistics_structure_legend_format</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>基于当前宝宝历史记录计算</t>
+          <t>%1$d次 · %2$d%%</t>
         </is>
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Based on this baby's history</t>
+          <t>%1$d times / %2$d%%</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
         <is>
-          <t>基於當前寶寶歷史記錄計算</t>
+          <t>%1$d次 · %2$d%%</t>
         </is>
       </c>
       <c r="E459" s="4" t="inlineStr">
         <is>
-          <t>現在の赤ちゃんの病歴に基づいて計算されます</t>
+          <t>%1$d 回 · %2$d%%</t>
         </is>
       </c>
       <c r="F459" s="4" t="inlineStr">
         <is>
-          <t>현재 아기 이력을 기준으로 계산됨</t>
+          <t>%1$d회 · %2$d%%</t>
         </is>
       </c>
       <c r="G459" s="4" t="n"/>
@@ -25299,32 +25299,32 @@
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_percentile_note_who</t>
+          <t>statistics_growth_percentile_title</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>基于 WHO 0-5 岁标准计算</t>
+          <t>成长曲线百分位</t>
         </is>
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Based on WHO 0-5 years standards</t>
+          <t>Growth percentiles</t>
         </is>
       </c>
       <c r="D460" s="4" t="inlineStr">
         <is>
-          <t>基於 WHO 0-5 歲標準計算</t>
+          <t>成長曲線百分位</t>
         </is>
       </c>
       <c r="E460" s="4" t="inlineStr">
         <is>
-          <t>0～5歳を対象としたWHO基準に基づいて算出</t>
+          <t>成長曲線のパーセンタイル</t>
         </is>
       </c>
       <c r="F460" s="4" t="inlineStr">
         <is>
-          <t>0~5세에 대한 WHO 기준에 따라 계산됨</t>
+          <t>성장 곡선 백분위수</t>
         </is>
       </c>
       <c r="G460" s="4" t="n"/>
@@ -25353,32 +25353,32 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_percentile_note_missing_info</t>
+          <t>statistics_growth_percentile_note</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>填写宝宝性别与生日后显示 WHO 百分位</t>
+          <t>基于当前宝宝历史记录计算</t>
         </is>
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Set gender and birthday to show WHO percentiles</t>
+          <t>Based on this baby's history</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
         <is>
-          <t>填寫寶寶性別與生日後顯示 WHO 百分位</t>
+          <t>基於當前寶寶歷史記錄計算</t>
         </is>
       </c>
       <c r="E461" s="4" t="inlineStr">
         <is>
-          <t>赤ちゃんの性別と誕生日を入力すると、WHOのパーセンタイルが表示されます。</t>
+          <t>現在の赤ちゃんの病歴に基づいて計算されます</t>
         </is>
       </c>
       <c r="F461" s="4" t="inlineStr">
         <is>
-          <t>아기의 성별과 생일을 입력하면 WHO 백분위수가 표시됩니다.</t>
+          <t>현재 아기 이력을 기준으로 계산됨</t>
         </is>
       </c>
       <c r="G461" s="4" t="n"/>
@@ -25407,32 +25407,32 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_percentile_empty</t>
+          <t>statistics_growth_percentile_note_who</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>暂无百分位</t>
+          <t>基于 WHO 0-5 岁标准计算</t>
         </is>
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>No percentile</t>
+          <t>Based on WHO 0-5 years standards</t>
         </is>
       </c>
       <c r="D462" s="4" t="inlineStr">
         <is>
-          <t>暫無百分位</t>
+          <t>基於 WHO 0-5 歲標準計算</t>
         </is>
       </c>
       <c r="E462" s="4" t="inlineStr">
         <is>
-          <t>まだパーセンタイルがありません</t>
+          <t>0～5歳を対象としたWHO基準に基づいて算出</t>
         </is>
       </c>
       <c r="F462" s="4" t="inlineStr">
         <is>
-          <t>아직 백분위수 없음</t>
+          <t>0~5세에 대한 WHO 기준에 따라 계산됨</t>
         </is>
       </c>
       <c r="G462" s="4" t="n"/>
@@ -25461,32 +25461,32 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>statistics_growth_percentile_rank_format</t>
+          <t>statistics_growth_percentile_note_missing_info</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>P%1$d</t>
+          <t>填写宝宝性别与生日后显示 WHO 百分位</t>
         </is>
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>P%1$d</t>
+          <t>Set gender and birthday to show WHO percentiles</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
         <is>
-          <t>P%1$d</t>
+          <t>填寫寶寶性別與生日後顯示 WHO 百分位</t>
         </is>
       </c>
       <c r="E463" s="4" t="inlineStr">
         <is>
-          <t>P%1$d</t>
+          <t>赤ちゃんの性別と誕生日を入力すると、WHOのパーセンタイルが表示されます。</t>
         </is>
       </c>
       <c r="F463" s="4" t="inlineStr">
         <is>
-          <t>P%1$d</t>
+          <t>아기의 성별과 생일을 입력하면 WHO 백분위수가 표시됩니다.</t>
         </is>
       </c>
       <c r="G463" s="4" t="n"/>
@@ -25515,32 +25515,32 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_title</t>
+          <t>statistics_growth_percentile_empty</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>健康与疫苗</t>
+          <t>暂无百分位</t>
         </is>
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Health &amp; vaccines</t>
+          <t>No percentile</t>
         </is>
       </c>
       <c r="D464" s="4" t="inlineStr">
         <is>
-          <t>健康與疫苗</t>
+          <t>暫無百分位</t>
         </is>
       </c>
       <c r="E464" s="4" t="inlineStr">
         <is>
-          <t>健康とワクチン</t>
+          <t>まだパーセンタイルがありません</t>
         </is>
       </c>
       <c r="F464" s="4" t="inlineStr">
         <is>
-          <t>건강과 백신</t>
+          <t>아직 백분위수 없음</t>
         </is>
       </c>
       <c r="G464" s="4" t="n"/>
@@ -25569,32 +25569,32 @@
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_range_format</t>
+          <t>statistics_growth_percentile_rank_format</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>统计范围：%1$s</t>
+          <t>P%1$d</t>
         </is>
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Range: %1$s</t>
+          <t>P%1$d</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
         <is>
-          <t>統計範圍：%1$s</t>
+          <t>P%1$d</t>
         </is>
       </c>
       <c r="E465" s="4" t="inlineStr">
         <is>
-          <t>統計範囲: %1$s</t>
+          <t>P%1$d</t>
         </is>
       </c>
       <c r="F465" s="4" t="inlineStr">
         <is>
-          <t>통계 범위: %1$s</t>
+          <t>P%1$d</t>
         </is>
       </c>
       <c r="G465" s="4" t="n"/>
@@ -25623,32 +25623,32 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_total_format</t>
+          <t>statistics_health_title</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>健康事件 %1$d次</t>
+          <t>健康与疫苗</t>
         </is>
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Health events %1$d times</t>
+          <t>Health &amp; vaccines</t>
         </is>
       </c>
       <c r="D466" s="4" t="inlineStr">
         <is>
-          <t>健康事件 %1$d次</t>
+          <t>健康與疫苗</t>
         </is>
       </c>
       <c r="E466" s="4" t="inlineStr">
         <is>
-          <t>健康関連イベント %1$d 回</t>
+          <t>健康とワクチン</t>
         </is>
       </c>
       <c r="F466" s="4" t="inlineStr">
         <is>
-          <t>건강 관련 이벤트 %1$d회</t>
+          <t>건강과 백신</t>
         </is>
       </c>
       <c r="G466" s="4" t="n"/>
@@ -25677,32 +25677,32 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_temperature_format</t>
+          <t>statistics_health_range_format</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>体温 %1$d次</t>
+          <t>统计范围：%1$s</t>
         </is>
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Temperature %1$d times</t>
+          <t>Range: %1$s</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
         <is>
-          <t>體溫 %1$d次</t>
+          <t>統計範圍：%1$s</t>
         </is>
       </c>
       <c r="E467" s="4" t="inlineStr">
         <is>
-          <t>体温%1$d回</t>
+          <t>統計範囲: %1$s</t>
         </is>
       </c>
       <c r="F467" s="4" t="inlineStr">
         <is>
-          <t>체온 %1$d회</t>
+          <t>통계 범위: %1$s</t>
         </is>
       </c>
       <c r="G467" s="4" t="n"/>
@@ -25731,32 +25731,32 @@
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_medicine_format</t>
+          <t>statistics_health_total_format</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>用药 %1$d次</t>
+          <t>健康事件 %1$d次</t>
         </is>
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Medicine %1$d times</t>
+          <t>Health events %1$d times</t>
         </is>
       </c>
       <c r="D468" s="4" t="inlineStr">
         <is>
-          <t>用藥 %1$d次</t>
+          <t>健康事件 %1$d次</t>
         </is>
       </c>
       <c r="E468" s="4" t="inlineStr">
         <is>
-          <t>%1$d回の投薬</t>
+          <t>健康関連イベント %1$d 回</t>
         </is>
       </c>
       <c r="F468" s="4" t="inlineStr">
         <is>
-          <t>약물 치료 %1$d회</t>
+          <t>건강 관련 이벤트 %1$d회</t>
         </is>
       </c>
       <c r="G468" s="4" t="n"/>
@@ -25785,32 +25785,32 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_doctor_format</t>
+          <t>statistics_health_temperature_format</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>就医 %1$d次</t>
+          <t>体温 %1$d次</t>
         </is>
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Doctor %1$d times</t>
+          <t>Temperature %1$d times</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
         <is>
-          <t>就醫 %1$d次</t>
+          <t>體溫 %1$d次</t>
         </is>
       </c>
       <c r="E469" s="4" t="inlineStr">
         <is>
-          <t>医療処置%1$d回</t>
+          <t>体温%1$d回</t>
         </is>
       </c>
       <c r="F469" s="4" t="inlineStr">
         <is>
-          <t>진료 %1$d회</t>
+          <t>체온 %1$d회</t>
         </is>
       </c>
       <c r="G469" s="4" t="n"/>
@@ -25839,32 +25839,32 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_symptom_format</t>
+          <t>statistics_health_medicine_format</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>症状 %1$d次</t>
+          <t>用药 %1$d次</t>
         </is>
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Symptoms %1$d times</t>
+          <t>Medicine %1$d times</t>
         </is>
       </c>
       <c r="D470" s="4" t="inlineStr">
         <is>
-          <t>症狀 %1$d次</t>
+          <t>用藥 %1$d次</t>
         </is>
       </c>
       <c r="E470" s="4" t="inlineStr">
         <is>
-          <t>症状が%1$d回発生</t>
+          <t>%1$d回の投薬</t>
         </is>
       </c>
       <c r="F470" s="4" t="inlineStr">
         <is>
-          <t>증상 %1$d회</t>
+          <t>약물 치료 %1$d회</t>
         </is>
       </c>
       <c r="G470" s="4" t="n"/>
@@ -25893,32 +25893,32 @@
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_vaccine_format</t>
+          <t>statistics_health_doctor_format</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>疫苗 %1$d次</t>
+          <t>就医 %1$d次</t>
         </is>
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Vaccines %1$d times</t>
+          <t>Doctor %1$d times</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
         <is>
-          <t>疫苗 %1$d次</t>
+          <t>就醫 %1$d次</t>
         </is>
       </c>
       <c r="E471" s="4" t="inlineStr">
         <is>
-          <t>ワクチンを%1$d回</t>
+          <t>医療処置%1$d回</t>
         </is>
       </c>
       <c r="F471" s="4" t="inlineStr">
         <is>
-          <t>백신 %1$d회</t>
+          <t>진료 %1$d회</t>
         </is>
       </c>
       <c r="G471" s="4" t="n"/>
@@ -25947,32 +25947,32 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_last_vaccine_format</t>
+          <t>statistics_health_symptom_format</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>上次接种：%1$s</t>
+          <t>症状 %1$d次</t>
         </is>
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Last shot: %1$s</t>
+          <t>Symptoms %1$d times</t>
         </is>
       </c>
       <c r="D472" s="4" t="inlineStr">
         <is>
-          <t>最後接種：%1$s</t>
+          <t>症狀 %1$d次</t>
         </is>
       </c>
       <c r="E472" s="4" t="inlineStr">
         <is>
-          <t>前回のワクチン接種: %1$s</t>
+          <t>症状が%1$d回発生</t>
         </is>
       </c>
       <c r="F472" s="4" t="inlineStr">
         <is>
-          <t>마지막 예방접종: %1$s</t>
+          <t>증상 %1$d회</t>
         </is>
       </c>
       <c r="G472" s="4" t="n"/>
@@ -26001,32 +26001,32 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>statistics_health_last_vaccine_empty</t>
+          <t>statistics_health_vaccine_format</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>暂无接种记录</t>
+          <t>疫苗 %1$d次</t>
         </is>
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>No vaccine record</t>
+          <t>Vaccines %1$d times</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
         <is>
-          <t>暫無接種紀錄</t>
+          <t>疫苗 %1$d次</t>
         </is>
       </c>
       <c r="E473" s="4" t="inlineStr">
         <is>
-          <t>ワクチン接種記録はまだありません</t>
+          <t>ワクチンを%1$d回</t>
         </is>
       </c>
       <c r="F473" s="4" t="inlineStr">
         <is>
-          <t>아직 예방접종 기록이 없습니다.</t>
+          <t>백신 %1$d회</t>
         </is>
       </c>
       <c r="G473" s="4" t="n"/>
@@ -26055,32 +26055,32 @@
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>statistics_day_record_count_format</t>
+          <t>statistics_health_last_vaccine_format</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>当天 %1$d 条记录</t>
+          <t>上次接种：%1$s</t>
         </is>
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>%1$d records that day</t>
+          <t>Last shot: %1$s</t>
         </is>
       </c>
       <c r="D474" s="4" t="inlineStr">
         <is>
-          <t>當天 %1$d 條記錄</t>
+          <t>最後接種：%1$s</t>
         </is>
       </c>
       <c r="E474" s="4" t="inlineStr">
         <is>
-          <t>当日 %1$d 件の記録</t>
+          <t>前回のワクチン接種: %1$s</t>
         </is>
       </c>
       <c r="F474" s="4" t="inlineStr">
         <is>
-          <t>해당 날짜 기록 %1$d개</t>
+          <t>마지막 예방접종: %1$s</t>
         </is>
       </c>
       <c r="G474" s="4" t="n"/>
@@ -26109,32 +26109,32 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>statistics_summary_other_scope</t>
+          <t>statistics_health_last_vaccine_empty</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>护理/活动/健康</t>
+          <t>暂无接种记录</t>
         </is>
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Care/activity/health</t>
+          <t>No vaccine record</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
         <is>
-          <t>護理/活動/健康</t>
+          <t>暫無接種紀錄</t>
         </is>
       </c>
       <c r="E475" s="4" t="inlineStr">
         <is>
-          <t>ケア/活動/健康</t>
+          <t>ワクチン接種記録はまだありません</t>
         </is>
       </c>
       <c r="F475" s="4" t="inlineStr">
         <is>
-          <t>케어/활동/건강</t>
+          <t>아직 예방접종 기록이 없습니다.</t>
         </is>
       </c>
       <c r="G475" s="4" t="n"/>
@@ -26163,32 +26163,32 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>statistics_insight_title</t>
+          <t>statistics_day_record_count_format</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>规律洞察</t>
+          <t>当天 %1$d 条记录</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Routine insights</t>
+          <t>%1$d records that day</t>
         </is>
       </c>
       <c r="D476" s="4" t="inlineStr">
         <is>
-          <t>規律洞察</t>
+          <t>當天 %1$d 條記錄</t>
         </is>
       </c>
       <c r="E476" s="4" t="inlineStr">
         <is>
-          <t>リズムの洞察</t>
+          <t>当日 %1$d 件の記録</t>
         </is>
       </c>
       <c r="F476" s="4" t="inlineStr">
         <is>
-          <t>패턴 인사이트</t>
+          <t>해당 날짜 기록 %1$d개</t>
         </is>
       </c>
       <c r="G476" s="4" t="n"/>
@@ -26217,32 +26217,32 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>statistics_insight_based_on_format</t>
+          <t>statistics_summary_other_scope</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>基于 %1$s</t>
+          <t>护理/活动/健康</t>
         </is>
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>Based on %1$s</t>
+          <t>Care/activity/health</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
         <is>
-          <t>基於 %1$s</t>
+          <t>護理/活動/健康</t>
         </is>
       </c>
       <c r="E477" s="4" t="inlineStr">
         <is>
-          <t>%1$s に基づく</t>
+          <t>ケア/活動/健康</t>
         </is>
       </c>
       <c r="F477" s="4" t="inlineStr">
         <is>
-          <t>%1$s 기준</t>
+          <t>케어/활동/건강</t>
         </is>
       </c>
       <c r="G477" s="4" t="n"/>
@@ -26271,32 +26271,32 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>statistics_until_selected_date_format</t>
+          <t>statistics_insight_title</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>截至 %1$s</t>
+          <t>规律洞察</t>
         </is>
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Until %1$s</t>
+          <t>Routine insights</t>
         </is>
       </c>
       <c r="D478" s="4" t="inlineStr">
         <is>
-          <t>截至 %1$s</t>
+          <t>規律洞察</t>
         </is>
       </c>
       <c r="E478" s="4" t="inlineStr">
         <is>
-          <t>%1$s まで</t>
+          <t>リズムの洞察</t>
         </is>
       </c>
       <c r="F478" s="4" t="inlineStr">
         <is>
-          <t>%1$s까지</t>
+          <t>패턴 인사이트</t>
         </is>
       </c>
       <c r="G478" s="4" t="n"/>
@@ -26325,32 +26325,32 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>statistics_load_failed</t>
+          <t>statistics_insight_based_on_format</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>加载失败</t>
+          <t>基于 %1$s</t>
         </is>
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>Load failed</t>
+          <t>Based on %1$s</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
         <is>
-          <t>載入失敗</t>
+          <t>基於 %1$s</t>
         </is>
       </c>
       <c r="E479" s="4" t="inlineStr">
         <is>
-          <t>読み込みに失敗しました</t>
+          <t>%1$s に基づく</t>
         </is>
       </c>
       <c r="F479" s="4" t="inlineStr">
         <is>
-          <t>로드 실패</t>
+          <t>%1$s 기준</t>
         </is>
       </c>
       <c r="G479" s="4" t="n"/>
@@ -26379,32 +26379,32 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>daily_records</t>
+          <t>statistics_until_selected_date_format</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>生活记录</t>
+          <t>截至 %1$s</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Daily records</t>
+          <t>Until %1$s</t>
         </is>
       </c>
       <c r="D480" s="4" t="inlineStr">
         <is>
-          <t>生活記錄</t>
+          <t>截至 %1$s</t>
         </is>
       </c>
       <c r="E480" s="4" t="inlineStr">
         <is>
-          <t>毎日の記録</t>
+          <t>%1$s まで</t>
         </is>
       </c>
       <c r="F480" s="4" t="inlineStr">
         <is>
-          <t>일상 기록</t>
+          <t>%1$s까지</t>
         </is>
       </c>
       <c r="G480" s="4" t="n"/>
@@ -26433,32 +26433,32 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>no_records_today</t>
+          <t>statistics_load_failed</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>这一天还没有记录</t>
+          <t>加载失败</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>There are no records for this day yet</t>
+          <t>Load failed</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
         <is>
-          <t>這一天還沒有記錄</t>
+          <t>載入失敗</t>
         </is>
       </c>
       <c r="E481" s="4" t="inlineStr">
         <is>
-          <t>この日の記録はまだありません</t>
+          <t>読み込みに失敗しました</t>
         </is>
       </c>
       <c r="F481" s="4" t="inlineStr">
         <is>
-          <t>아직 이 날의 기록이 없습니다.</t>
+          <t>로드 실패</t>
         </is>
       </c>
       <c r="G481" s="4" t="n"/>
@@ -26487,32 +26487,32 @@
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
         <is>
-          <t>add_record</t>
+          <t>daily_records</t>
         </is>
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>添加记录</t>
+          <t>生活记录</t>
         </is>
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Add record</t>
+          <t>Daily records</t>
         </is>
       </c>
       <c r="D482" s="4" t="inlineStr">
         <is>
-          <t>新增記錄</t>
+          <t>生活記錄</t>
         </is>
       </c>
       <c r="E482" s="4" t="inlineStr">
         <is>
-          <t>レコードの追加</t>
+          <t>毎日の記録</t>
         </is>
       </c>
       <c r="F482" s="4" t="inlineStr">
         <is>
-          <t>레코드 추가</t>
+          <t>일상 기록</t>
         </is>
       </c>
       <c r="G482" s="4" t="n"/>
@@ -26541,32 +26541,32 @@
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>diaper</t>
+          <t>no_records_today</t>
         </is>
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>尿布</t>
+          <t>这一天还没有记录</t>
         </is>
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>Diaper</t>
+          <t>There are no records for this day yet</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
         <is>
-          <t>尿布</t>
+          <t>這一天還沒有記錄</t>
         </is>
       </c>
       <c r="E483" s="4" t="inlineStr">
         <is>
-          <t>おむつ</t>
+          <t>この日の記録はまだありません</t>
         </is>
       </c>
       <c r="F483" s="4" t="inlineStr">
         <is>
-          <t>기저귀</t>
+          <t>아직 이 날의 기록이 없습니다.</t>
         </is>
       </c>
       <c r="G483" s="4" t="n"/>
@@ -26595,32 +26595,32 @@
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>count_times</t>
+          <t>add_record</t>
         </is>
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>%d次</t>
+          <t>添加记录</t>
         </is>
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>%d times</t>
+          <t>Add record</t>
         </is>
       </c>
       <c r="D484" s="4" t="inlineStr">
         <is>
-          <t>%d次</t>
+          <t>新增記錄</t>
         </is>
       </c>
       <c r="E484" s="4" t="inlineStr">
         <is>
-          <t>%d 回</t>
+          <t>レコードの追加</t>
         </is>
       </c>
       <c r="F484" s="4" t="inlineStr">
         <is>
-          <t>%d회</t>
+          <t>레코드 추가</t>
         </is>
       </c>
       <c r="G484" s="4" t="n"/>
@@ -26649,32 +26649,32 @@
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
         <is>
-          <t>duration_format_short</t>
+          <t>diaper</t>
         </is>
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>%1$dh%2$dm</t>
+          <t>尿布</t>
         </is>
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>%1$dh%2$dm</t>
+          <t>Diaper</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
         <is>
-          <t>%1$dh%2$dm</t>
+          <t>尿布</t>
         </is>
       </c>
       <c r="E485" s="4" t="inlineStr">
         <is>
-          <t>%1$dh%2$dm</t>
+          <t>おむつ</t>
         </is>
       </c>
       <c r="F485" s="4" t="inlineStr">
         <is>
-          <t>%1$dh%2$dm</t>
+          <t>기저귀</t>
         </is>
       </c>
       <c r="G485" s="4" t="n"/>
@@ -26703,32 +26703,32 @@
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
         <is>
-          <t>left_side</t>
+          <t>count_times</t>
         </is>
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>左侧</t>
+          <t>%d次</t>
         </is>
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>left side</t>
+          <t>%d times</t>
         </is>
       </c>
       <c r="D486" s="4" t="inlineStr">
         <is>
-          <t>左側</t>
+          <t>%d次</t>
         </is>
       </c>
       <c r="E486" s="4" t="inlineStr">
         <is>
-          <t>左側</t>
+          <t>%d 回</t>
         </is>
       </c>
       <c r="F486" s="4" t="inlineStr">
         <is>
-          <t>왼쪽</t>
+          <t>%d회</t>
         </is>
       </c>
       <c r="G486" s="4" t="n"/>
@@ -26757,32 +26757,32 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>right_side</t>
+          <t>duration_format_short</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>右侧</t>
+          <t>%1$dh%2$dm</t>
         </is>
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>right side</t>
+          <t>%1$dh%2$dm</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
         <is>
-          <t>右側</t>
+          <t>%1$dh%2$dm</t>
         </is>
       </c>
       <c r="E487" s="4" t="inlineStr">
         <is>
-          <t>右側</t>
+          <t>%1$dh%2$dm</t>
         </is>
       </c>
       <c r="F487" s="4" t="inlineStr">
         <is>
-          <t>오른쪽</t>
+          <t>%1$dh%2$dm</t>
         </is>
       </c>
       <c r="G487" s="4" t="n"/>
@@ -26811,32 +26811,32 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>duration_min</t>
+          <t>left_side</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>%d分钟</t>
+          <t>左侧</t>
         </is>
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>%d minutes</t>
+          <t>left side</t>
         </is>
       </c>
       <c r="D488" s="4" t="inlineStr">
         <is>
-          <t>%d分鐘</t>
+          <t>左側</t>
         </is>
       </c>
       <c r="E488" s="4" t="inlineStr">
         <is>
-          <t>%d分</t>
+          <t>左側</t>
         </is>
       </c>
       <c r="F488" s="4" t="inlineStr">
         <is>
-          <t>%d분</t>
+          <t>왼쪽</t>
         </is>
       </c>
       <c r="G488" s="4" t="n"/>
@@ -26865,32 +26865,32 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>amount_ml</t>
+          <t>right_side</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>%dml</t>
+          <t>右侧</t>
         </is>
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>%dml</t>
+          <t>right side</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
         <is>
-          <t>%dml</t>
+          <t>右側</t>
         </is>
       </c>
       <c r="E489" s="4" t="inlineStr">
         <is>
-          <t>%dml</t>
+          <t>右側</t>
         </is>
       </c>
       <c r="F489" s="4" t="inlineStr">
         <is>
-          <t>%dml</t>
+          <t>오른쪽</t>
         </is>
       </c>
       <c r="G489" s="4" t="n"/>
@@ -26919,32 +26919,32 @@
     <row r="490">
       <c r="A490" s="4" t="inlineStr">
         <is>
-          <t>sleep_started</t>
+          <t>duration_min</t>
         </is>
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>开始睡觉</t>
+          <t>%d分钟</t>
         </is>
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>Started sleeping</t>
+          <t>%d minutes</t>
         </is>
       </c>
       <c r="D490" s="4" t="inlineStr">
         <is>
-          <t>開始睡覺</t>
+          <t>%d分鐘</t>
         </is>
       </c>
       <c r="E490" s="4" t="inlineStr">
         <is>
-          <t>睡眠開始</t>
+          <t>%d分</t>
         </is>
       </c>
       <c r="F490" s="4" t="inlineStr">
         <is>
-          <t>수면 시작</t>
+          <t>%d분</t>
         </is>
       </c>
       <c r="G490" s="4" t="n"/>
@@ -26973,32 +26973,32 @@
     <row r="491">
       <c r="A491" s="4" t="inlineStr">
         <is>
-          <t>sleep_ended</t>
+          <t>amount_ml</t>
         </is>
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>睡醒了</t>
+          <t>%dml</t>
         </is>
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>Woke up</t>
+          <t>%dml</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
         <is>
-          <t>睡醒了</t>
+          <t>%dml</t>
         </is>
       </c>
       <c r="E491" s="4" t="inlineStr">
         <is>
-          <t>起床</t>
+          <t>%dml</t>
         </is>
       </c>
       <c r="F491" s="4" t="inlineStr">
         <is>
-          <t>깨어남</t>
+          <t>%dml</t>
         </is>
       </c>
       <c r="G491" s="4" t="n"/>
@@ -27027,32 +27027,32 @@
     <row r="492">
       <c r="A492" s="4" t="inlineStr">
         <is>
-          <t>sleep_in_progress</t>
+          <t>sleep_started</t>
         </is>
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>睡眠中</t>
+          <t>开始睡觉</t>
         </is>
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>Sleeping</t>
+          <t>Started sleeping</t>
         </is>
       </c>
       <c r="D492" s="4" t="inlineStr">
         <is>
-          <t>睡眠中</t>
+          <t>開始睡覺</t>
         </is>
       </c>
       <c r="E492" s="4" t="inlineStr">
         <is>
-          <t>睡眠中</t>
+          <t>睡眠開始</t>
         </is>
       </c>
       <c r="F492" s="4" t="inlineStr">
         <is>
-          <t>수면 중</t>
+          <t>수면 시작</t>
         </is>
       </c>
       <c r="G492" s="4" t="n"/>
@@ -27079,1216 +27079,1324 @@
       <c r="AB492" s="4" t="n"/>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>baby_gender_boy_label</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>♂ 男孩</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>♂ Boy</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>♂ 男孩</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>♂ 男の子</t>
-        </is>
-      </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>♂ 남아</t>
-        </is>
-      </c>
+      <c r="A493" s="4" t="inlineStr">
+        <is>
+          <t>sleep_ended</t>
+        </is>
+      </c>
+      <c r="B493" s="4" t="inlineStr">
+        <is>
+          <t>睡醒了</t>
+        </is>
+      </c>
+      <c r="C493" s="4" t="inlineStr">
+        <is>
+          <t>Woke up</t>
+        </is>
+      </c>
+      <c r="D493" s="4" t="inlineStr">
+        <is>
+          <t>睡醒了</t>
+        </is>
+      </c>
+      <c r="E493" s="4" t="inlineStr">
+        <is>
+          <t>起床</t>
+        </is>
+      </c>
+      <c r="F493" s="4" t="inlineStr">
+        <is>
+          <t>깨어남</t>
+        </is>
+      </c>
+      <c r="G493" s="4" t="n"/>
+      <c r="H493" s="4" t="n"/>
+      <c r="I493" s="4" t="n"/>
+      <c r="J493" s="4" t="n"/>
+      <c r="K493" s="4" t="n"/>
+      <c r="L493" s="4" t="n"/>
+      <c r="M493" s="4" t="n"/>
+      <c r="N493" s="4" t="n"/>
+      <c r="O493" s="4" t="n"/>
+      <c r="P493" s="4" t="n"/>
+      <c r="Q493" s="4" t="n"/>
+      <c r="R493" s="4" t="n"/>
+      <c r="S493" s="4" t="n"/>
+      <c r="T493" s="4" t="n"/>
+      <c r="U493" s="4" t="n"/>
+      <c r="V493" s="4" t="n"/>
+      <c r="W493" s="4" t="n"/>
+      <c r="X493" s="4" t="n"/>
+      <c r="Y493" s="4" t="n"/>
+      <c r="Z493" s="4" t="n"/>
+      <c r="AA493" s="4" t="n"/>
+      <c r="AB493" s="4" t="n"/>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>baby_gender_girl_label</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>♀ 女孩</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>♀ Girl</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>♀ 女孩</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>♀ 女の子</t>
-        </is>
-      </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>♀ 여아</t>
-        </is>
-      </c>
+      <c r="A494" s="4" t="inlineStr">
+        <is>
+          <t>sleep_in_progress</t>
+        </is>
+      </c>
+      <c r="B494" s="4" t="inlineStr">
+        <is>
+          <t>睡眠中</t>
+        </is>
+      </c>
+      <c r="C494" s="4" t="inlineStr">
+        <is>
+          <t>Sleeping</t>
+        </is>
+      </c>
+      <c r="D494" s="4" t="inlineStr">
+        <is>
+          <t>睡眠中</t>
+        </is>
+      </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>睡眠中</t>
+        </is>
+      </c>
+      <c r="F494" s="4" t="inlineStr">
+        <is>
+          <t>수면 중</t>
+        </is>
+      </c>
+      <c r="G494" s="4" t="n"/>
+      <c r="H494" s="4" t="n"/>
+      <c r="I494" s="4" t="n"/>
+      <c r="J494" s="4" t="n"/>
+      <c r="K494" s="4" t="n"/>
+      <c r="L494" s="4" t="n"/>
+      <c r="M494" s="4" t="n"/>
+      <c r="N494" s="4" t="n"/>
+      <c r="O494" s="4" t="n"/>
+      <c r="P494" s="4" t="n"/>
+      <c r="Q494" s="4" t="n"/>
+      <c r="R494" s="4" t="n"/>
+      <c r="S494" s="4" t="n"/>
+      <c r="T494" s="4" t="n"/>
+      <c r="U494" s="4" t="n"/>
+      <c r="V494" s="4" t="n"/>
+      <c r="W494" s="4" t="n"/>
+      <c r="X494" s="4" t="n"/>
+      <c r="Y494" s="4" t="n"/>
+      <c r="Z494" s="4" t="n"/>
+      <c r="AA494" s="4" t="n"/>
+      <c r="AB494" s="4" t="n"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>baby_age_days_format</t>
+          <t>baby_gender_boy_label</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>%1$d天</t>
+          <t>♂ 男孩</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>%1$d days</t>
+          <t>♂ Boy</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>%1$d天</t>
+          <t>♂ 男孩</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>%1$d日</t>
+          <t>♂ 男の子</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>%1$d일</t>
+          <t>♂ 남아</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>baby_info_gender_age_format</t>
+          <t>baby_gender_girl_label</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>%1$s · %2$s</t>
+          <t>♀ 女孩</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>%1$s · %2$s</t>
+          <t>♀ Girl</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>%1$s · %2$s</t>
+          <t>♀ 女孩</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>%1$s · %2$s</t>
+          <t>♀ 女の子</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>%1$s · %2$s</t>
+          <t>♀ 여아</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>baby_birth_date_format</t>
+          <t>baby_age_days_format</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>出生: %1$s</t>
+          <t>%1$d天</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Born: %1$s</t>
+          <t>%1$d days</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>出生：%1$s</t>
+          <t>%1$d天</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>誕生日: %1$s</t>
+          <t>%1$d日</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>출생: %1$s</t>
+          <t>%1$d일</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>calendar_month_title_pattern</t>
+          <t>baby_info_gender_age_format</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>yyyy年M月</t>
+          <t>%1$s · %2$s</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>MMMM yyyy</t>
+          <t>%1$s · %2$s</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>yyyy年M月</t>
+          <t>%1$s · %2$s</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>yyyy年M月</t>
+          <t>%1$s · %2$s</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>yyyy년 M월</t>
+          <t>%1$s · %2$s</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>calendar_week_title_format</t>
+          <t>baby_birth_date_format</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>%1$s 第%2$d周</t>
+          <t>出生: %1$s</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>%1$s Week %2$d</t>
+          <t>Born: %1$s</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>%1$s 第%2$d週</t>
+          <t>出生：%1$s</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>%1$s 第%2$d週</t>
+          <t>誕生日: %1$s</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>%1$s %2$d주차</t>
+          <t>출생: %1$s</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>calendar_weekday_sunday_short</t>
+          <t>calendar_month_title_pattern</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>yyyy年M月</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>MMMM yyyy</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>yyyy年M月</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>yyyy年M月</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>yyyy년 M월</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>calendar_weekday_monday_short</t>
+          <t>calendar_week_title_format</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>%1$s 第%2$d周</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>%1$s Week %2$d</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>一</t>
+          <t>%1$s 第%2$d週</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>%1$s 第%2$d週</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>%1$s %2$d주차</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>calendar_weekday_tuesday_short</t>
+          <t>calendar_weekday_sunday_short</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>二</t>
+          <t>日</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>일</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>calendar_weekday_wednesday_short</t>
+          <t>calendar_weekday_monday_short</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>一</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>一</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>calendar_weekday_thursday_short</t>
+          <t>calendar_weekday_tuesday_short</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>四</t>
+          <t>二</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>화</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>calendar_weekday_friday_short</t>
+          <t>calendar_weekday_wednesday_short</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>五</t>
+          <t>三</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>수</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>calendar_weekday_saturday_short</t>
+          <t>calendar_weekday_thursday_short</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>六</t>
+          <t>四</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>六</t>
+          <t>四</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>summary_duration_hours_minutes_compact</t>
+          <t>calendar_weekday_friday_short</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>%1$d小时%2$d分</t>
+          <t>五</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>%1$dH %2$dm</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>%1$d小時%2$d分</t>
+          <t>五</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>%1$d時間%2$d分</t>
+          <t>金</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>%1$d시간 %2$d분</t>
+          <t>금</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>summary_duration_hours_compact</t>
+          <t>calendar_weekday_saturday_short</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>%1$d小时</t>
+          <t>六</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>%1$dH</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>%1$d小時</t>
+          <t>六</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>%1$d時間</t>
+          <t>土</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>%1$d시간</t>
+          <t>토</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>summary_duration_minutes_compact</t>
+          <t>summary_duration_hours_minutes_compact</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>%1$d分</t>
+          <t>%1$d小时%2$d分</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>%1$dm</t>
+          <t>%1$dH %2$dm</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>%1$d分</t>
+          <t>%1$d小時%2$d分</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>%1$d分</t>
+          <t>%1$d時間%2$d分</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>%1$d분</t>
+          <t>%1$d시간 %2$d분</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>summary_duration_zero_compact</t>
+          <t>summary_duration_hours_compact</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>0分</t>
+          <t>%1$d小时</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>%1$dH</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>0分</t>
+          <t>%1$d小時</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>0分</t>
+          <t>%1$d時間</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>0분</t>
+          <t>%1$d시간</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>summary_diaper_wet_count_short</t>
+          <t>summary_duration_minutes_compact</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>湿%1$d</t>
+          <t>%1$d分</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Wet %1$d</t>
+          <t>%1$dm</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>濕%1$d</t>
+          <t>%1$d分</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>おしっこ%1$d</t>
+          <t>%1$d分</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>젖음 %1$d</t>
+          <t>%1$d분</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>summary_diaper_dirty_count_short</t>
+          <t>summary_duration_zero_compact</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>脏%1$d</t>
+          <t>0分</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Dirty %1$d</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>髒%1$d</t>
+          <t>0分</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>うんち%1$d</t>
+          <t>0分</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>대변 %1$d</t>
+          <t>0분</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>summary_diaper_mixed_count_short</t>
+          <t>summary_diaper_wet_count_short</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>混合%1$d</t>
+          <t>湿%1$d</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Mixed %1$d</t>
+          <t>Wet %1$d</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>混合%1$d</t>
+          <t>濕%1$d</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>混合%1$d</t>
+          <t>おしっこ%1$d</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>혼합 %1$d</t>
+          <t>젖음 %1$d</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>event_record_date_title_pattern</t>
+          <t>summary_diaper_dirty_count_short</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>M月d日 E</t>
+          <t>脏%1$d</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>MMM d, E</t>
+          <t>Dirty %1$d</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>M月d日 E</t>
+          <t>髒%1$d</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>M月d日 E</t>
+          <t>うんち%1$d</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>M월 d일 E</t>
+          <t>대변 %1$d</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>relative_time_just_now</t>
+          <t>summary_diaper_mixed_count_short</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>刚刚</t>
+          <t>混合%1$d</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Just now</t>
+          <t>Mixed %1$d</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>剛剛</t>
+          <t>混合%1$d</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>たった今</t>
+          <t>混合%1$d</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>방금</t>
+          <t>혼합 %1$d</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>relative_time_minutes_ago_format</t>
+          <t>event_record_date_title_pattern</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>%1$d分钟前</t>
+          <t>M月d日 E</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>%1$d minutes ago</t>
+          <t>MMM d, E</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>%1$d分鐘前</t>
+          <t>M月d日 E</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>%1$d分前</t>
+          <t>M月d日 E</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>%1$d분 전</t>
+          <t>M월 d일 E</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>relative_time_minutes_later_format</t>
+          <t>relative_time_just_now</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>%1$d分钟后</t>
+          <t>刚刚</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>in %1$d minutes</t>
+          <t>Just now</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>%1$d分鐘後</t>
+          <t>剛剛</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>%1$d分後</t>
+          <t>たった今</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>%1$d분 후</t>
+          <t>방금</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>relative_time_hours_ago_format</t>
+          <t>relative_time_minutes_ago_format</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>%1$d小时前</t>
+          <t>%1$d分钟前</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>%1$d hours ago</t>
+          <t>%1$d minutes ago</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>%1$d小時前</t>
+          <t>%1$d分鐘前</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>%1$d時間前</t>
+          <t>%1$d分前</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>%1$d시간 전</t>
+          <t>%1$d분 전</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>relative_time_hours_later_format</t>
+          <t>relative_time_minutes_later_format</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>%1$d小时后</t>
+          <t>%1$d分钟后</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>in %1$d hours</t>
+          <t>in %1$d minutes</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>%1$d小時後</t>
+          <t>%1$d分鐘後</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>%1$d時間後</t>
+          <t>%1$d分後</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>%1$d시간 후</t>
+          <t>%1$d분 후</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>relative_time_days_ago_format</t>
+          <t>relative_time_hours_ago_format</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>%1$d天前</t>
+          <t>%1$d小时前</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>%1$d days ago</t>
+          <t>%1$d hours ago</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>%1$d天前</t>
+          <t>%1$d小時前</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>%1$d日前</t>
+          <t>%1$d時間前</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>%1$d일 전</t>
+          <t>%1$d시간 전</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>relative_time_days_later_format</t>
+          <t>relative_time_hours_later_format</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>%1$d天后</t>
+          <t>%1$d小时后</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>in %1$d days</t>
+          <t>in %1$d hours</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>%1$d天後</t>
+          <t>%1$d小時後</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>%1$d日後</t>
+          <t>%1$d時間後</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>%1$d일 후</t>
+          <t>%1$d시간 후</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>relative_time_months_ago_format</t>
+          <t>relative_time_days_ago_format</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>%1$d个月前</t>
+          <t>%1$d天前</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>%1$d months ago</t>
+          <t>%1$d days ago</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>%1$d個月前</t>
+          <t>%1$d天前</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>%1$dか月前</t>
+          <t>%1$d日前</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>%1$d개월 전</t>
+          <t>%1$d일 전</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>relative_time_months_later_format</t>
+          <t>relative_time_days_later_format</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>%1$d个月后</t>
+          <t>%1$d天后</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>in %1$d months</t>
+          <t>in %1$d days</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>%1$d個月後</t>
+          <t>%1$d天後</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>%1$dか月後</t>
+          <t>%1$d日後</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>%1$d개월 후</t>
+          <t>%1$d일 후</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>baby_profile_new_title</t>
+          <t>relative_time_months_ago_format</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>新宝宝档案</t>
+          <t>%1$d个月前</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>New baby profile</t>
+          <t>%1$d months ago</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>新寶寶檔案</t>
+          <t>%1$d個月前</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>新しい赤ちゃんのプロフィール</t>
+          <t>%1$dか月前</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>새 아기 프로필</t>
+          <t>%1$d개월 전</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>baby_profile_create_subtitle</t>
+          <t>relative_time_months_later_format</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>姓名是唯一必填项</t>
+          <t>%1$d个月后</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Name is the only required field</t>
+          <t>in %1$d months</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>姓名是唯一必填項</t>
+          <t>%1$d個月後</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>名前だけが必須です</t>
+          <t>%1$dか月後</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>이름만 필수 항목입니다</t>
+          <t>%1$d개월 후</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>baby_profile_basic_info</t>
+          <t>baby_profile_new_title</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>基础信息</t>
+          <t>新宝宝档案</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Basic information</t>
+          <t>New baby profile</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>基本資訊</t>
+          <t>新寶寶檔案</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>基本情報</t>
+          <t>新しい赤ちゃんのプロフィール</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>기본 정보</t>
+          <t>새 아기 프로필</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>baby_profile_birth_info</t>
+          <t>baby_profile_create_subtitle</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>出生信息</t>
+          <t>姓名是唯一必填项</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Birth details</t>
+          <t>Name is the only required field</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>出生資訊</t>
+          <t>姓名是唯一必填項</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>出生情報</t>
+          <t>名前だけが必須です</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>출생 정보</t>
+          <t>이름만 필수 항목입니다</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>baby_profile_select_birthday</t>
+          <t>baby_profile_basic_info</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>选择生日</t>
+          <t>基础信息</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Select birthday</t>
+          <t>Basic information</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>選擇生日</t>
+          <t>基本資訊</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>誕生日を選択</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>생일 선택</t>
+          <t>기본 정보</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>please_select</t>
+          <t>baby_profile_birth_info</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>请选择</t>
+          <t>出生信息</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Please select</t>
+          <t>Birth details</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>請選擇</t>
+          <t>出生資訊</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>選択してください</t>
+          <t>出生情報</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>선택해 주세요</t>
+          <t>출생 정보</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
+          <t>baby_profile_select_birthday</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>选择生日</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Select birthday</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>選擇生日</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>誕生日を選択</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>생일 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>please_select</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>请选择</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Please select</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>請選擇</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>選択してください</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>선택해 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B532" t="inlineStr">
         <is>
           <t>可选</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C532" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
+      <c r="D532" t="inlineStr">
         <is>
           <t>可選</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr">
+      <c r="E532" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr">
+      <c r="F532" t="inlineStr">
         <is>
           <t>선택 사항</t>
         </is>
